--- a/4_fine_tune_und_verbesserung/4_training_data/ground_truth_filtered.xlsx
+++ b/4_fine_tune_und_verbesserung/4_training_data/ground_truth_filtered.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O805"/>
+  <dimension ref="A1:P805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,11 @@
           <t>Headline_GER</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -541,6 +546,11 @@
           <t>Robert Mueller III lässt seinen Fall ruhen – die Demokraten werden es NIEMALS tun</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -590,6 +600,11 @@
           <t>Robert Mueller empfiehlt keine weiteren Anklagen</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -639,6 +654,11 @@
           <t>„Besonderer Platz in der Hölle“ für diejenigen, die den Brexit ohne Plan befürworteten – Tusk von der EU</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -688,6 +708,11 @@
           <t>Bill Maher sagt, er brauche keinen Mueller-Bericht, um zu wissen, dass Trump ein Verräter ist, „weil er einen Fernseher hat“</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -737,6 +762,11 @@
           <t>Ausbruch in Madagaskar: Es ist „unvermeidlich“, dass die Pest gegen Medikamente resistent wird</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -786,6 +816,11 @@
           <t>Wie gefällt es Ihnen, für Vergleiche wegen sexueller Belästigung durch Ihren Kongress in Amerika zu bezahlen?</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -835,6 +870,11 @@
           <t>Ehemaliger Apostolischer Nuntius in den Vereinigten Staaten beschuldigt Papst der McCarrick-Vertuschung und fordert Franziskus zum Rücktritt auf</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -884,6 +924,11 @@
           <t>Neuer Ebola-Ausbruch tötet 17 im Nordwesten der DR Kongo</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -933,6 +978,11 @@
           <t>Die gegen einen jüdischen Studentenpolitiker gerichtete Abstimmung war nicht antisemitisch: Bericht von McGill</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -982,6 +1032,11 @@
           <t>Die iranische Aggression verschärft sich</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1031,6 +1086,11 @@
           <t>Hier sind alle Vorwürfe wegen sexuellen Fehlverhaltens gegen Senator Al Franken</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1080,6 +1140,11 @@
           <t>Liebe „Karawane“ illegaler Ausländer: Sagen Sie „Hola“ zu Trumps RAZOR Wire</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1129,6 +1194,11 @@
           <t>Von Trump begnadigter ehemaliger Marinesoldat sagt, er verklagt Comey und Obama</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1178,6 +1248,11 @@
           <t>Machst du Witze, Ted Cruz? Geben Sie nicht dem Polizisten die Schuld, der zugegeben hat, Botham Jean getötet zu haben?</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1227,6 +1302,11 @@
           <t>WHO bereitet sich auf den „schlimmsten Fall“ vor, da sich der Ebola-Ausbruch im Kongo ausbreitet</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1276,6 +1356,11 @@
           <t>Gary Wills, Autor der törichten Religion: „Die Religion des Korans ist eine Religion des Friedens“</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1325,6 +1410,11 @@
           <t>Britische Labour Party: Wir haben Pamela Geller verboten, jetzt wollen wir auch Trump verbieten</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1374,6 +1464,11 @@
           <t>Tee mit dem Pfarrer: Der Angriff auf die Ehe ist ein Angriff auf Christus in der Eucharistie</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1423,6 +1518,11 @@
           <t>Vom Schlechten zum Schlimmeren? Tillerson raus – CIA-Direktor Pompeo rein im Außenministerium – Gina Haspel als CIA-Chefin</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1472,6 +1572,11 @@
           <t>Die Polizei war zuvor zu dem Haus gegangen, wo Streifenpolizisten in Ohio getötet wurden</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1521,6 +1626,11 @@
           <t>Kavanaughs Nominierung gespeichert?</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1570,6 +1680,11 @@
           <t>US-Richter lässt auf Anordnung von Trump festgehaltenen indonesischen Einwanderer frei</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1619,6 +1734,11 @@
           <t>Der Schauprozess der Linken für Kavanaugh</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1668,6 +1788,11 @@
           <t>Dokumente: Auf einem Gelände in New Mexico festgenommene Muslime trainierten Kinder, Schießereien in der Schule durchzuführen</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1717,6 +1842,11 @@
           <t>Ist die Auslöschung der Menschheit vorhersehbar? Weltgesundheitschef: Globale Pandemie steht unmittelbar bevor</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1766,6 +1896,11 @@
           <t>Teenager, dem der MAGA-Hut vom Kopf gerissen wurde, bekommt einen neuen, von Trump signierten Hut</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1815,6 +1950,11 @@
           <t>Ebola-Ausbruch in der Demokratischen Republik Kongo gemeldet</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1864,6 +2004,11 @@
           <t>Es gab „aktive Schützen auf der Landebahn“ – bombastische Flugsicherungs-Audioaufnahmen aus der Nacht des Las Vegas-Massakers enthüllten</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1913,6 +2058,11 @@
           <t>Von Soros finanzierte Anwälte helfen Wohnwagenmigranten, in den Vereinigten Staaten Asyl zu bekommen</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1962,6 +2112,11 @@
           <t>Beichtvater eines Augenzeugen: Während des Massakers in Las Vegas gab es einen aktiven Schützen, der das Bellagio Hotel ins Visier nahm</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2011,6 +2166,11 @@
           <t>Trump entlässt Tillerson und ersetzt ihn durch einen ehemaligen Top-Spion</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2060,6 +2220,11 @@
           <t>BEWEIS: Das LVMPD und das FBI haben es versäumt, mindestens ein verstorbenes Opfer des Las Vegas-Massakers zu katalogisieren, da die Zahl der Todesopfer steigt</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2109,6 +2274,11 @@
           <t>Trump zu Sitzungen in einer Reihe von Tweets: „Stoppt die manipulierte Hexenjagd JETZT!“</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2158,6 +2328,11 @@
           <t>Verschwörung: Muslimischer Fotograf und Nation Of Islam versteckten seit 2008 Fotos von Obama und Farrakhan</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2207,6 +2382,11 @@
           <t>Trump droht mit militärischer Schließung der US-Grenze, um Migranten aufzuhalten</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2256,6 +2436,11 @@
           <t>Der schwulenfeindliche Imam war erneut bei der Gala der Demokraten in Florida vertreten</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2305,6 +2490,11 @@
           <t>Trump drückt Reality Winner sein Mitgefühl aus, dessen Mutter um Verzeihung bittet</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2354,6 +2544,11 @@
           <t>Heute vor 54 Jahren: Regierung und Medien haben „Fake News“ erstellt und verbreitet, um den Vietnamkrieg auszulösen</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2403,6 +2598,11 @@
           <t>Frankreich erteilt muslimischem Mörder einer älteren jüdischen Frau einen Passierschein</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2452,6 +2652,11 @@
           <t>Krankenhäuser in Madagaskar in höchster Alarmbereitschaft: „Niemand ist sicher“ vor der schwarzen Pest</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2501,6 +2706,11 @@
           <t>Trump nominiert Gina Haspel offiziell zur nächsten CIA-Direktorin</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2550,6 +2760,11 @@
           <t>Blaues Privileg: Amber Guyger gegen Kaution frei, da Aktivistinnen friedlich gegen ihre Verrottung im Gefängnis protestierten</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2599,6 +2814,11 @@
           <t>Imam, dessen Sohn Schulschützen trainierte, attackiert Reporter auf dem Gelände von New Mexico: „Sie hassen den Islam“</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2648,6 +2868,11 @@
           <t>Der Kongressabgeordnete der Demokraten korrigiert die Behauptung der ADL, er stehe nicht auf Farrakhan</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2697,6 +2922,11 @@
           <t>„Vertuschungsbrief“ aus Chile widerspricht Papst</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2746,6 +2976,11 @@
           <t>CNN verklagt Trump mit der Forderung, Jim Acostas Ausweis im Weißen Haus wiederherzustellen</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2795,6 +3030,11 @@
           <t>Sodom und Gomorra wurden von Gott gerichtet, weil die Menschen sich weigerten, seine Gebote im Umgang mit den Bösen zu halten!</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2844,6 +3084,11 @@
           <t>Keith Ellison, Ankläger wegen häuslicher Gewalt: Die Demokratische Partei glaubt meiner Geschichte nicht</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2893,6 +3138,11 @@
           <t>Ungarischer Premierminister: „Das Christentum ist Europas letzte Hoffnung“</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2942,6 +3192,11 @@
           <t>Erschreckende Details veröffentlicht: Neue Anklage gegen zwei dschihadistische Muslime auf tödlichem islamischem Gelände in New Mexico</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2991,6 +3246,11 @@
           <t>Stacey Abrams verklagt Georgia wegen „grober Misswirtschaft“ bei Wahlen</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3040,6 +3300,11 @@
           <t>ZUM ERSTEN MAL ONLINE: Die prophetische Ansprache von Erzbischof Lefebvre an den Überrest, 1976</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3089,6 +3354,11 @@
           <t>Der Tod von Kate Steinle durch einen mexikanischen Staatsbürger wurde zu einem Brennpunkt in der Einwanderungsdebatte – hier ist die Geschichte hinter ihrer Ermordung</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3138,6 +3408,11 @@
           <t>Die Pest ist in der Luft und breitet sich aus, weil die Menschen buchstäblich „mit Leichen tanzen“</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3187,6 +3462,11 @@
           <t>Student sagt, Antisemitismus sei immer noch ein Problem in der McGill-Studentenregierung</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3236,6 +3516,11 @@
           <t>Verurteilt „schändliches Urteil“, nachdem die Jury in San Francisco den „Kate’s Law“-Opfermörder freigesprochen hat</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3285,6 +3570,11 @@
           <t>Untersuchung im Konsulatsverletzungsvorwurf findet keine Hinweise</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3334,6 +3624,11 @@
           <t>Der beschuldigte Frauenmissbraucher Keith Ellison bittet die Ethikabteilung des Repräsentantenhauses um eine Untersuchung</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3383,6 +3678,11 @@
           <t>Iran gibt zu, Al-Qaida unterstützt und Dschihad-Terroranschläge vom 11. September ermöglicht zu haben</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3432,6 +3732,11 @@
           <t>Eine weitere solide Waffe, mit der US-Diplomaten angegriffen werden: Dieses Mal in China</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3481,6 +3786,11 @@
           <t>Neue Audioaufnahmen aus der Nacht des Las Vegas-Massakers zeigen, dass es während des Angriffs „einen weiteren aktiven Schützen“ in der Bar oben im Mandalay Bay Hotel gab</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3530,6 +3840,11 @@
           <t>Die von Rücktritten und Kritik betroffene Kommission für sexuellen Missbrauch von Papst Franziskus erhält einen Neustart</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3579,6 +3894,11 @@
           <t>Neu veröffentlichtes privates Überwachungsmaterial vom Massaker in Las Vegas zeigt „über dem Kopf schwebende Hubschrauber“ während des Angriffs</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3628,6 +3948,11 @@
           <t>Der neue Schwarm des muslimischen Verbrechensbekämpfers Sofian Zakkout: der antisemitische Pastor Steve Anderson</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3677,6 +4002,11 @@
           <t>Bestätigt: Behörden haben bezüglich des Check-in-Datums im Hotel des Attentäters in Las Vegas gelogen – was verschweigen sie sonst noch?</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3726,6 +4056,11 @@
           <t>Mann wurde verhaftet, weil er am Tatort des 911-Auflegens angeblich eine Waffe gekauft hatte, mit der Polizisten aus Ohio getötet wurden</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3775,6 +4110,11 @@
           <t>Kardinal Burke an Michael Matt: „Amoris ist keine Ausübung des Lehramtes“ (Was nun?)</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3824,6 +4164,11 @@
           <t>Ungarns Orban fordert eine globale Anti-Migranten-Allianz mit Blick auf die Wahlen 2018</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3873,6 +4218,11 @@
           <t>Das vorsätzlich ignorante FBI kann das Motiv für den muslimischen Dschihadisten, der auf der Travis Air Force Base in Propangastanks fuhr, nicht herausfinden</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3922,6 +4272,11 @@
           <t>Wir sollten mehr wie Schweden sein: Die Regierung könnte die Armee gegen Einwandererbanden einsetzen</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3971,6 +4326,11 @@
           <t>Jüdische und pro-israelische Studenten haben den Universitätsrat wegen ihres Widerstands gegen BDS vor Gericht gestellt</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4020,6 +4380,11 @@
           <t>Warum die Leakerin des Weißen Hauses, Dina Habib Powell „McMaster’s Huma Abedin“, nicht UN-Botschafterin sein sollte</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4069,6 +4434,11 @@
           <t>Bill Clinton: „Öffentliche Entschuldigung bei Monica Lewinsky war genug“</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4118,6 +4488,11 @@
           <t>Der nächste Pestausbruch in Madagaskar könnte „stärker“ ausfallen: WHO</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4167,6 +4542,11 @@
           <t>Großbritannien: Labour-Abgeordneter zitiert das Verbot von Robert Spencer und Pamela Geller und fordert, dass Trump aus dem Land verbannt wird</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4216,6 +4596,11 @@
           <t>Brasilianischer Waffenhändler in den USA festgenommen</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4265,6 +4650,11 @@
           <t>Der ICE-Einsatz in West-Michigan führt innerhalb von vier Tagen zu 16 Festnahmen</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4314,6 +4704,11 @@
           <t>Skeptisch gegenüber dokumentierten Lügnern zu sein, die einen Kandidaten für den Obersten Gerichtshof angreifen, ist eine gute Sache – hier ist der Grund dafür</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4363,6 +4758,11 @@
           <t>Das Weiße Haus legt einen Verhaltenskodex für die Presse des Weißen Hauses vor – wenn diese nicht funktionieren, werden sie gezwungen sein, mehr zu schreiben</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4412,6 +4812,11 @@
           <t>Die Zahl der Einwohner Puerto Ricos ohne sauberes Wasser und Strom steigt weiter</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4461,6 +4866,11 @@
           <t>Don Lemon lügt ... Wieder einmal: Die größte Bedrohung sind nicht „weiße Männer“ – die meistgesuchten inländischen Terroristen des FBI sind diese Leute</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4510,6 +4920,11 @@
           <t>Aufzeichnungen stützen Behauptungen, dass der Abgeordnete des Staates Minnesota Muslima, Ilhan Omar, ihren Bruder geheiratet hat</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4559,6 +4974,11 @@
           <t>Schock! Der Papst greift nun offen Opfer sexuellen Kindesmissbrauchs wegen „Verleumdung“ an</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4608,6 +5028,11 @@
           <t>SONDERBERICHT: Angebliche Vertuschung durch den Papst, Anklage gegen Papst in internationalem Fall von sexuellem Missbrauch</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4657,6 +5082,11 @@
           <t>Kongo bestätigt zwei Ebola-Fälle und meldet Ausbruch</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4706,6 +5136,11 @@
           <t>Der katholische Bischof entfernt die Namen seiner Vorgänger aus Kirchengebäuden, weil sie es versäumt haben, Kinder zu schützen</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4755,6 +5190,11 @@
           <t>Homeschooling schützt Kinder vor Gewalt und Marxismus</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4804,6 +5244,11 @@
           <t>Menschen fordern das Weiße Haus auf, die Oregon Ranchers Steve und Dwight Hammond zu begnadigen</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4853,6 +5298,11 @@
           <t>Obama war nie so hart gegenüber Russland wie Trump</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4902,6 +5352,11 @@
           <t>Bill Clinton besteht darauf, dass er Monica Lewinsky keine Entschuldigung schuldet</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4951,6 +5406,11 @@
           <t>„Glaubhafte Beweise für eine terroristische Infiltration“: Kongressabgeordneter sagt, „geheime Informationen“ beweisen ISIS-Verbindung zum Massaker in Las Vegas</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5000,6 +5460,11 @@
           <t>Der kommende Putsch</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5049,6 +5514,11 @@
           <t>Zehnter Bischof unterzeichnet „Bekenntnis unveränderlicher Wahrheiten“ zur Verteidigung der Ehe</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5098,6 +5568,11 @@
           <t>Ebola-Ausbruch in der Demokratischen Republik Kongo bestätigt</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5147,6 +5622,11 @@
           <t>GOP-Bericht: Die Obama-Administration hat daran gearbeitet, dem Iran den Austausch von Milliarden zu ermöglichen, um Sanktionen zu umgehen</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5196,6 +5676,11 @@
           <t>Gesetzgeber macht schockierende Behauptung zum Massaker in Las Vegas (Video)</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5245,6 +5730,11 @@
           <t>Die Zahl der Todesopfer im Ramadan-Dschihad 2018 liegt bisher bei 218</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5294,6 +5784,11 @@
           <t>Wie viele Kindesvergewaltiger hat der Bürgermeister von Sanctuary City verraten?</t>
         </is>
       </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5343,6 +5838,11 @@
           <t>Juanita Broaddrick: Senator Feinstein hatte kein Interesse an meinem Vergewaltigungsvorwurf</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -5392,6 +5892,11 @@
           <t>Opfer der Schießerei in Las Vegas: „Es gab 100 % mehr als einen Schützen“, die Tore zum Konzert wurden kurz vor dem Anschlag verschlossen</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5441,6 +5946,11 @@
           <t>Mit 3D-gedruckten Waffen ist das Blutvergießen nur einen Klick entfernt</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5490,6 +6000,11 @@
           <t>ICE verhaftet 20 Personen in Kansas City während einer viertägigen Operation gegen kriminelle Ausländer</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5539,6 +6054,11 @@
           <t>Die demokratische Senatskandidatin von Arizona, Kyrsten Sinema, weigert sich, ihren Antrag zurückzuziehen, und sagt, es sei in Ordnung, wenn Amerikaner sich den Taliban anschließen</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5588,6 +6108,11 @@
           <t>Ein Polizist aus Ohio tötete die Frau des Verdächtigen und versteckte sich im Gebüsch, während sein Ehemann auf Polizisten schoss, wie der Notruf zeigt</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5637,6 +6162,11 @@
           <t>Warnung vor dem Schwarzen Tod: Die Pest lässt sich nicht ausrotten</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5686,6 +6216,11 @@
           <t>Keine Gerechtigkeit für Kate Steinle</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5735,6 +6270,11 @@
           <t>Huch! Sogar John McCain ist besorgt über Trumps Wahl für die CIA</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5784,6 +6324,11 @@
           <t>Großbritannien verbietet Aktivisten für freie Meinungsäußerung und nimmt gleichzeitig zahlreiche Prediger von Dschihad-Gewalt, Hass und Scharia auf</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5833,6 +6378,11 @@
           <t>Senator Lindsey Graham entfesselt einen Feuersturm auf demokratische Senatoren wegen der „unethischsten Täuschung“, seit er in der Politik ist</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5882,6 +6432,11 @@
           <t>ANSEHEN: John Bolton verspricht, dass die USA den Iran bis 2019 in einem Raum voller „ehemaliger Terroristen“ „stürzen“ würden</t>
         </is>
       </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5931,6 +6486,11 @@
           <t>Das DOJ schlägt möglicherweise den #Resistance-Bürgermeister vor, der illegale Kriminelle wegen Behinderung der Justiz gewarnt hat</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5980,6 +6540,11 @@
           <t>Israel nimmt es mit dem schiitischen Halbmond auf</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6029,6 +6594,11 @@
           <t>Bundesrichter setzt sich über das Justizministerium hinweg und verstößt gegen den ersten Verfassungszusatz: Blockiert 3D-gedruckte Waffenpläne</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6078,6 +6648,11 @@
           <t>Die Islamisierung der öffentlichen Schulen</t>
         </is>
       </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6127,6 +6702,11 @@
           <t>Anwalt: Munitionshändler hat bei dem Täter in Las Vegas nichts Verdächtiges gesehen</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6176,6 +6756,11 @@
           <t>Der Pestausbruch in Madagaskar hat bereits 57 Todesopfer gefordert und über 600 infiziert</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6225,6 +6810,11 @@
           <t>Papst gibt zu, dass die katholische Kirche das Problem des Kindesmissbrauchs „lange ignoriert“ hat</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6274,6 +6864,11 @@
           <t>Der Mörder einer französischen Jüdin wurde in der zweiten Beurteilung für unfähig befunden, sich vor Gericht zu verantworten</t>
         </is>
       </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -6323,6 +6918,11 @@
           <t>Kongressabgeordneter: „Glaubhafte Beweise“ für „terroristische Infiltration über die Südgrenze“ im Zusammenhang mit Schießerei in Las Vegas</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -6372,6 +6972,11 @@
           <t>Die Polizei war zuvor zu einem Haus in Ohio gegangen, wo Beamte getötet wurden</t>
         </is>
       </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -6421,6 +7026,11 @@
           <t>Kardinal Theodore McCarrick: Noch eine Frucht des Zweiten Vatikanischen Konzils</t>
         </is>
       </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -6470,6 +7080,11 @@
           <t>Hillary macht einen rassistischen Witz, nachdem sie Cory Booker und Eric Holder verwechselt hat: „Sie sehen alle gleich aus“</t>
         </is>
       </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -6519,6 +7134,11 @@
           <t>Fortsetzung des Schauprozesses in San Francisco</t>
         </is>
       </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -6568,6 +7188,11 @@
           <t>Der österreichische Bischof lehnt die Idee der deutschen Bischöfe, homosexuelle Partnerschaften zu segnen, energisch ab</t>
         </is>
       </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -6617,6 +7242,11 @@
           <t>Google hat mit Clintons Wahlkampf mit „stillen Spenden“ zusammengearbeitet</t>
         </is>
       </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6666,6 +7296,11 @@
           <t>DOJ kapituliert: 3D-Druck-Waffenakten sind durch den ersten Verfassungszusatz geschützt</t>
         </is>
       </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6715,6 +7350,11 @@
           <t>J Street „Kapos“ könnte demokratischen Abgeordneten wegen „jüdischer Frage“ nicht unterstützen</t>
         </is>
       </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6764,6 +7404,11 @@
           <t>Der Versuch der Polizei von Dallas, Botham Jean wegen einer winzigen Menge Gras zu „beschmieren“, scheiterte kläglich</t>
         </is>
       </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6813,6 +7458,11 @@
           <t>Illegaler Ausländer, der wegen versuchten Mordes in North Carolina gesucht wird, an der Grenze zwischen den USA und Mexiko festgenommen</t>
         </is>
       </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -6862,6 +7512,11 @@
           <t>Lokale Polizei und Fed verhängen Informationssperre bei Schießerei in Las Vegas</t>
         </is>
       </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6911,6 +7566,11 @@
           <t>Die von Gott selbst eingeführte Todesstrafe (die biblische Grundlage für die katholische Lehre zur Todesstrafe)</t>
         </is>
       </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6960,6 +7620,11 @@
           <t>Zeuge: Der IT-Berater der muslimischen Demokraten, Awan, hat sie abgehört, dann wurde das von ihr kontrollierte Bankkonto geleert</t>
         </is>
       </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7009,6 +7674,11 @@
           <t>Der Justizausschuss des Senats stimmt für die Nominierung von Kavanaugh</t>
         </is>
       </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7058,6 +7728,11 @@
           <t>Hat Trump die Tür geöffnet?</t>
         </is>
       </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7107,6 +7782,11 @@
           <t>Demokratische Republik Kongo: Neuer Ebola-Ausbruch fordert zwei Todesopfer in der Provinz Equateur</t>
         </is>
       </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7156,6 +7836,11 @@
           <t>Ungarischer Ministerpräsident bringt es auf den Punkt: Flüchtlinge seien in Wirklichkeit „muslimische Eindringlinge“</t>
         </is>
       </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -7205,6 +7890,11 @@
           <t>Gegen Kamala Harris und Elizabeth Warren wurde im Senat eine Ethikbeschwerde eingereicht</t>
         </is>
       </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -7254,6 +7944,11 @@
           <t>Obama-Richter entscheidet, Wahl in Georgia zu ändern</t>
         </is>
       </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -7303,6 +7998,11 @@
           <t>Trump: „Wenn Sie nicht die Worte ‚Sprecher Pelosi‘ sagen wollen … gehen Sie raus und wählen Sie“</t>
         </is>
       </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -7352,6 +8052,11 @@
           <t>„Stille Spende“: Unternehmens-E-Mails enthüllen, dass Google-Führungskräfte versucht haben, Latino-Wähler zu gewinnen, von denen sie glaubten, dass sie für Clinton stimmen würden</t>
         </is>
       </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -7401,6 +8106,11 @@
           <t>FBI: Muslimischer Teenager aus islamischem Gelände in New Mexico für den Dschihad ausgebildet: „Eine Armee aufstellen“ „Ungläubige im Namen Allahs töten“</t>
         </is>
       </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -7450,6 +8160,11 @@
           <t>Rand Paul sagt, er werde Trumps Kandidaten für die CIA und das Außenministerium ablehnen</t>
         </is>
       </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -7499,6 +8214,11 @@
           <t>Was passiert nach der islamischen Eroberung?</t>
         </is>
       </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -7548,6 +8268,11 @@
           <t>Zwei Männer und Mütter verhaftet, nachdem Kind tot aufgefunden wurde, 11 weitere in „schmutzigem“ Gelände in New Mexico zusammen mit bewaffneten „muslimischen Extremisten“ gefunden</t>
         </is>
       </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -7597,6 +8322,11 @@
           <t>Homeschooling weitet sich aus, da Eltern über liberale Sozialmanipulation und Gewalt sauer werden</t>
         </is>
       </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -7646,6 +8376,11 @@
           <t>Trump fordert Sessions auf, Muellers Russland-Ermittlungen zu stoppen, was das Gespenst einer versuchten Behinderung aufkommen lässt</t>
         </is>
       </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -7695,6 +8430,11 @@
           <t>Sarsours Mentor, der Bombenanschlag auf das WTC und eine Schießerei in einer Schule in New Mexico</t>
         </is>
       </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -7744,6 +8484,11 @@
           <t>Eine antisemitische Säuberung an der McGill University</t>
         </is>
       </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7793,6 +8538,11 @@
           <t>Illegale ausländische Frauenschläger, die vom Bürgermeister von Sanctuary City geschützt werden, aufgeflogen</t>
         </is>
       </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -7842,6 +8592,11 @@
           <t>Terrorist der Travis Air Force Base als Muslim Hafiz Kazi identifiziert</t>
         </is>
       </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -7891,6 +8646,11 @@
           <t>Der Brennan-Rosenstein-Mueller-Comey-Pressitut</t>
         </is>
       </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -7940,6 +8700,11 @@
           <t>Wenn Kavanaugh vom Senat nicht bestätigt wird, sind wir alle nur noch eine Anklage vom Ruin entfernt</t>
         </is>
       </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7989,6 +8754,11 @@
           <t>Erster amerikanischer Staatsbürger, der wegen Beitritts zu ISIS verurteilt wurde, wird zu 20 Jahren Haft verurteilt</t>
         </is>
       </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8038,6 +8808,11 @@
           <t>Ilhan Omar, Kongresskandidat der Pro-Scharia-Demokraten, verteidigt Tweet zu „bösen Taten Israels“</t>
         </is>
       </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8087,6 +8862,11 @@
           <t>Bischof Morlino nimmt die „homosexuelle Subkultur“ in der Kirche ins Visier und fordert Wiedergutmachung für das Heilige Herz Jesu</t>
         </is>
       </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -8136,6 +8916,11 @@
           <t>Wer hat den Trump-Kim-Gipfel „gewonnen“?</t>
         </is>
       </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8185,6 +8970,11 @@
           <t>Erzbischof Viganò spricht, die Neo-Katholiken geraten in Panik</t>
         </is>
       </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -8234,6 +9024,11 @@
           <t>Kardinal O’Malley wird die wiederbelebte Missbrauchskommission des Vatikans leiten</t>
         </is>
       </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -8283,6 +9078,11 @@
           <t>„Wir haben jetzt urbanes Ebola“ im Kongo, WHO warnt vor „potenziell explosionsartigem Anstieg“ der Fälle</t>
         </is>
       </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8332,6 +9132,11 @@
           <t>„Emotionale und körperliche Misshandlung“: Der stellvertretende DNC-Vorsitzende der Muslimbruderschaft Ellison, Ankläger, veröffentlicht einen Arztbericht, in dem er als mutmaßlicher Täter benannt wird</t>
         </is>
       </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -8381,6 +9186,11 @@
           <t>Anschauen: Campus Commie hat einen mit Obszönitäten beladenen, zischenden Anfall und schüttet Getränke über FSU-Republikaner aus</t>
         </is>
       </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8430,6 +9240,11 @@
           <t>Nigel Farage warnt: „Wir werden einen Kampf zwischen dem Westen und dem Islam verlieren“.</t>
         </is>
       </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8479,6 +9294,11 @@
           <t>Die tödliche Pest könnte mutieren und unbehandelbar werden, wenn sie sich weltweit ausbreitet</t>
         </is>
       </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -8528,6 +9348,11 @@
           <t>Das Gericht ordnet an, dass das Weiße Haus die Presseberechtigung des CNN-Korrespondenten Jim Acosta wiederherstellen muss</t>
         </is>
       </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -8577,6 +9402,11 @@
           <t>EXPERIMENTELLER Ebola-Impfstoff wird im Kongo verabreicht, da die Zahl der Ebola-Todesopfer steigt</t>
         </is>
       </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -8626,6 +9456,11 @@
           <t>Der Ausfall des Stromnetzes in Rico führt zu einer Gesundheitskrise epischen Ausmaßes</t>
         </is>
       </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -8675,6 +9510,11 @@
           <t>Indien schließt sich den USA und China an und plant, den Mond zu besuchen</t>
         </is>
       </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -8724,6 +9564,11 @@
           <t>ICE deportiert guatemaltekischen Mann, der wegen Mordes gesucht wird</t>
         </is>
       </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -8773,6 +9618,11 @@
           <t>Mueller sei „auf der Suche nach Ärger“, sagt Trump kryptisch</t>
         </is>
       </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -8822,6 +9672,11 @@
           <t>Der verzweifelte Feinstein drängt auf 30 Jahre alte Behauptung wegen sexuellen Fehlverhaltens von Kavanaugh</t>
         </is>
       </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -8871,6 +9726,11 @@
           <t>Trump-Effekt: Islamische Republik stellt Marine-Provokationen im Arabischen Golf ein</t>
         </is>
       </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -8920,6 +9780,11 @@
           <t>SONDERBERICHT: Papst Franziskus wird Untätigkeit in Fällen berüchtigten sexuellen Missbrauchs vorgeworfen</t>
         </is>
       </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -8969,6 +9834,11 @@
           <t>Trump schlägt vor, dass er einen anderen Generalstaatsanwalt ausgewählt hätte, der die Russland-Ermittlungen hätte blockieren können</t>
         </is>
       </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -9018,6 +9888,11 @@
           <t>Facebook-Verbotsentwurf zur Verhinderung dschihadistischer Angriffe auf Amerikaner.</t>
         </is>
       </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9067,6 +9942,11 @@
           <t>Ist Präsident Trump ein Verräter?</t>
         </is>
       </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -9116,6 +9996,11 @@
           <t>Schlechter Verlierer: Stacey Abrams beendet Herausforderungen im Rennen um den Gouverneursposten in Georgia – wird nicht zugeben – will Klage einreichen</t>
         </is>
       </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -9165,6 +10050,11 @@
           <t>Papst Franziskus prangert „mörderische Gleichgültigkeit“ gegenüber der Christenverfolgung an, deren Hauptverantwortlicher er ist</t>
         </is>
       </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -9214,6 +10104,11 @@
           <t>Virginia: Muslim wird zu 20 Jahren Haft verurteilt, weil er sich ISIS angeschlossen hat, und sagt, er habe jeden Tag acht Stunden lang den Islam studiert</t>
         </is>
       </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -9263,6 +10158,11 @@
           <t>Die Demokraten wollen, dass wir allen Frauen glauben … es sei denn, sie beschuldigen Keith Ellison, Bill Clinton, Al Franken oder George Soros</t>
         </is>
       </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -9312,6 +10212,11 @@
           <t>Deutscher Kardinal: Liturgischer „Segen“ für Schwulengemeinschaften ist „wirklich … Sakrileg“</t>
         </is>
       </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -9361,6 +10266,11 @@
           <t>„Sie sehen alle gleich aus“ – Hillary macht nach Booker/Holder-Verwechslung einen rassistischen Witz</t>
         </is>
       </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -9410,6 +10320,11 @@
           <t>Vertuschung des Massakers in Las Vegas: Der Gerichtsmediziner von Clark County veröffentlicht 58 Autopsieberichte mit geschwärzten Namen, ohne Ballistik und ohne Stephen Paddock-Autopsie</t>
         </is>
       </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9459,6 +10374,11 @@
           <t>Papst Franziskus: Ross Douthat und Massimo Faggioli diskutieren über die Zukunft der katholischen Kirche</t>
         </is>
       </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -9508,6 +10428,11 @@
           <t>Obama versuchte heimlich, Banken dazu zu bringen, dem Iran zu helfen, doch die Banken weigerten sich</t>
         </is>
       </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -9557,6 +10482,11 @@
           <t>Der ungarische Ministerpräsident Viktor Orban fordert eine globale Anti-Migranten-Allianz</t>
         </is>
       </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -9606,6 +10536,11 @@
           <t>ICE verhaftet 145 Personen in Süd- und Zentraltexas während einer siebentägigen Operation gegen kriminelle Ausländer</t>
         </is>
       </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -9655,6 +10590,11 @@
           <t>Patrick J. Buchanan: Boehners Rechte – jetzt ist Trumps Partei | Artikel</t>
         </is>
       </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -9704,6 +10644,11 @@
           <t>Präsident Donald Trump schlägt „einfachen Einwanderungsplan“ vor: Illegale müssen gehen!</t>
         </is>
       </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -9753,6 +10698,11 @@
           <t>Polizist aus Dallas schließlich verhaftet, nachdem er falsche Wohnung betreten und einen Mann getötet hatte</t>
         </is>
       </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -9802,6 +10752,11 @@
           <t>Puerto Rico soll 16 Milliarden US-Dollar an staatlicher Katastrophenhilfe erhalten</t>
         </is>
       </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -9851,6 +10806,11 @@
           <t>9 Schritte zur erfolgreichen Bekämpfung des Dschihad</t>
         </is>
       </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -9900,6 +10860,11 @@
           <t>Veränderte Wahlunterlagen im Zusammenhang mit Demokraten in Florida von der Bundesanwaltschaft überprüft</t>
         </is>
       </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -9949,6 +10914,11 @@
           <t>Die Hammond-Begnadigungen bringen Gerechtigkeit für Obamas Opfer</t>
         </is>
       </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9998,6 +10968,11 @@
           <t>Dritthöchster demokratischer Bürgerrechtsheld erschien mit Farrakhan, wird nicht verurteilen</t>
         </is>
       </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -10047,6 +11022,11 @@
           <t>Trumps Plan für den Iran: Terroristen an die Macht bringen?</t>
         </is>
       </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -10096,6 +11076,11 @@
           <t>Polizei wegen „widrigen Verhaltens“ feuert schließlich Amber Guyger wegen Mordes an Botham Jean</t>
         </is>
       </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -10145,6 +11130,11 @@
           <t>Der Diktator-Papst: Ein Aufruf zur hierarchischen Opposition</t>
         </is>
       </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -10194,6 +11184,11 @@
           <t>Beamte warnen: Die Epidemie des Schwarzen Todes in der Luft könnte „explodieren“</t>
         </is>
       </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -10243,6 +11238,11 @@
           <t>Der Anwalt des Kavanaugh-Anklägers ist stellvertretender Vorsitzender der von Soros finanzierten Organisation, die sich gegen Kavanaugh stellt</t>
         </is>
       </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -10292,6 +11292,11 @@
           <t>Texas: Polizist betritt das Haus, von dem sie dachte, es gehöre ihr, und tötet einen unschuldigen Hausbesitzer – wird aber nicht verhaftet</t>
         </is>
       </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -10341,6 +11346,11 @@
           <t>Chefin von Dallas sagt, dass sie Amber Guyger nicht entlassen kann, weil sie Botham Jean getötet hat – die Regeln des Ministeriums deuten auf etwas anderes hin</t>
         </is>
       </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -10390,6 +11400,11 @@
           <t>Demokratischer Kongressabgeordneter lobt Hitler-liebenden Antisemiten</t>
         </is>
       </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -10439,6 +11454,11 @@
           <t>Beende den Koreakrieg!</t>
         </is>
       </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -10488,6 +11508,11 @@
           <t>Neues Virus ohne Heilung: Das ist schlimmer als der „Schwarze Tod“</t>
         </is>
       </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -10537,6 +11562,11 @@
           <t>Zwei TRÄUME wurden beim Schmuggel illegaler Ausländer erwischt</t>
         </is>
       </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -10586,6 +11616,11 @@
           <t>Paar fragt sich, warum die Polizei so lange mit der Durchsuchung des Geländes in New Mexico gewartet hat</t>
         </is>
       </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -10635,6 +11670,11 @@
           <t>Bundesrichter entscheidet gegen Trump-Regierung im Fall eines 3-D-Waffenbauplans</t>
         </is>
       </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -10684,6 +11724,11 @@
           <t>Schock: Patienten mit schwarzem Tod fliehen aus Angst vor Nadeln aus dem Krankenhaus, da die Beamten befürchten, dass sich die Pest ausbreiten könnte</t>
         </is>
       </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -10733,6 +11778,11 @@
           <t>Top-Wahlbeamter des Florida County ließ Menschen illegal per Fax und E-Mail abstimmen</t>
         </is>
       </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -10782,6 +11832,11 @@
           <t>Viganò verdoppelt sich und beschuldigt Franziskus, Christus aus den Augen verloren zu haben</t>
         </is>
       </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -10831,6 +11886,11 @@
           <t>Bundesanwälte wurden eingeschaltet, nachdem Demokraten in Florida die Manipulation von Wahlunterlagen erwischt hatten</t>
         </is>
       </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -10880,6 +11940,11 @@
           <t>Ich sage, was Kavanaugh nicht sagen würde: Christine Ford war Teil des politischen Anschlags auf ihn und hier ist der Audiobeweis</t>
         </is>
       </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -10929,6 +11994,11 @@
           <t>Kann sich die Kirche gegen Bergoglio wehren?</t>
         </is>
       </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -10978,6 +12048,11 @@
           <t>US-Bürgermeisterkonferenz fordert mehr Gesetze zur Waffenbeschlagnahme</t>
         </is>
       </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -11027,6 +12102,11 @@
           <t>Muslimischer Geistlicher: „Es gab Juden in islamischen Ländern und Kalifaten, aber wir haben sie nie getötet, nur weil sie Juden waren“</t>
         </is>
       </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -11076,6 +12156,11 @@
           <t>Kavanaugh und Last-Minute-Anschuldigungen</t>
         </is>
       </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -11125,6 +12210,11 @@
           <t>Armeeoberst: „Vorfall im Golf von Tonkin“ unter falscher Flagge könnte genutzt werden, um die USA in einen Krieg mit dem Iran zu verwickeln</t>
         </is>
       </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -11174,6 +12264,11 @@
           <t>MSM nutzt den Kavanaugh-Sexskandal, um Sie vom wahren Grund abzulenken, warum er nicht bestätigt werden sollte</t>
         </is>
       </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -11223,6 +12318,11 @@
           <t>FBI-Informant „bedroht“, nachdem er Details preisgegeben hatte, die die Clinton-Stiftung mit dem russischen Bestechungsfall in Verbindung bringen</t>
         </is>
       </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -11272,6 +12372,11 @@
           <t>Hat der heilige Franziskus Papst Franziskus vorhergesagt?</t>
         </is>
       </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -11321,6 +12426,11 @@
           <t>Ex-Seemann von Trump begnadigt, verklagt Obama und Comey, weil sie Hillary NICHT strafrechtlich verfolgt haben</t>
         </is>
       </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -11370,6 +12480,11 @@
           <t>Schwarzer Tod: „Es ist 100 % wahrscheinlich“, dass er sich nach Großbritannien ausbreitet und eine „tickende Zeitbombe“ ist, die bereit ist, die Welt zu dezimieren</t>
         </is>
       </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -11419,6 +12534,11 @@
           <t>ICE entfernt guatemaltekischen Staatsangehörigen, der wegen Mordes gesucht wird</t>
         </is>
       </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -11468,6 +12588,11 @@
           <t>Richter befiehlt dem Weißen Haus, den Presseausweis von Jim Acosta wiederherzustellen – Trump antwortet</t>
         </is>
       </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -11517,6 +12642,11 @@
           <t>Jeff Sessions schlägt auf Trump zurück</t>
         </is>
       </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -11566,6 +12696,11 @@
           <t>Keith Ellison, Unterstützer des Polizistenmörders, ruft die Polizei, um ihn vor einer mit Mikrofon und Kamerahandy bewaffneten Journalistin zu schützen</t>
         </is>
       </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -11615,6 +12750,11 @@
           <t>Scorecard: Sehen Sie, ob Ihr Vertreter oder Senator den zweiten Verfassungszusatz unterstützt oder nicht</t>
         </is>
       </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -11664,6 +12804,11 @@
           <t>Kardinal Müller: Die Segnung homosexueller Paare wäre eine „Gräueltat“</t>
         </is>
       </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -11713,6 +12858,11 @@
           <t>Unglaublich! Scharia New Mexico: Islamische Dschihadisten werden nach Anklage wegen „Islamophobie“ und „Rassismus“ auf Kaution freigelassen (Islam ist keine Rasse)</t>
         </is>
       </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -11762,6 +12912,11 @@
           <t>Es geht wieder los – durchgesickerte Dokumente: Das Weiße Haus plant einen Regimewechsel im Iran</t>
         </is>
       </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -11811,6 +12966,11 @@
           <t>Verteidiger der New-Mexico-Dschihadisten: „Wenn das weiße Christen wären … würde niemand mit der Wimper zucken“</t>
         </is>
       </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -11860,6 +13020,11 @@
           <t>Paul Manafort traf sich heimlich mit Julian Assange, kurz bevor er sich Trumps Präsidentschaftswahlkampf anschloss: Bericht</t>
         </is>
       </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -11909,6 +13074,11 @@
           <t>Mitglied der MS-503-Gang von Grenzschutzbeamten in Arizona festgenommen</t>
         </is>
       </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -11958,6 +13128,11 @@
           <t>Ehemalige muslimische Katholiken an Papst Franziskus: „Naivität gegenüber dem Islam ist selbstmörderisch und sehr gefährlich“</t>
         </is>
       </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -12007,6 +13182,11 @@
           <t>Kommunistischer Türsteher greift jugendlichen Trump-Anhänger an</t>
         </is>
       </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -12056,6 +13236,11 @@
           <t>Amerikaner in China bei „Schallangriff“ ähnlich wie in Kuba verletzt</t>
         </is>
       </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -12105,6 +13290,11 @@
           <t>Nationale Daten | Jobs im Dezember – TRUMP-EFFEKT! Die Vertreibung amerikanischer Arbeitnehmer, die Einwandererbevölkerung und die Arbeitslosigkeit der Schwarzen gehen zurück! | Artikel</t>
         </is>
       </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -12154,6 +13344,11 @@
           <t>Von Trump begnadigter Ex-Seemann sagt, er verklage Obama und Comey</t>
         </is>
       </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -12203,6 +13398,11 @@
           <t>Hören Sie auf, die Demokraten zu beschwichtigen</t>
         </is>
       </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -12252,6 +13452,11 @@
           <t>Was Sie im Notfall tun sollten: „Was ist Ihr Beruf?“</t>
         </is>
       </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -12301,6 +13506,11 @@
           <t>Die Polizei von Dallas entlässt einen Beamten, der Botham Jean in seiner Wohnung getötet hat</t>
         </is>
       </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -12350,6 +13560,11 @@
           <t>Haftbefehle zeigen, dass die Polizei Amber Guygers Wohnung nie durchsucht hat, jetzt ist es zu spät, sie hat sie „geräumt“.</t>
         </is>
       </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -12399,6 +13614,11 @@
           <t>Durchgesickertes Dokument enthüllt, dass das Weiße Haus einen „Regimewechsel“ im Iran plant</t>
         </is>
       </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -12448,6 +13668,11 @@
           <t>Es ist in der Luft: Beamte warnen, dass sich die Seuche „Schwarzer Tod“ schnell ausbreiten könnte</t>
         </is>
       </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -12497,6 +13722,11 @@
           <t>Trump begnadigt Hammonds!</t>
         </is>
       </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -12546,6 +13776,11 @@
           <t>Die Anschuldigungen wegen häuslicher Gewalt gegen Keith Ellison seien nicht stichhaltig, sagt der Anwalt der Demokraten</t>
         </is>
       </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -12595,6 +13830,11 @@
           <t>Trump verspricht, Acosta von CNN erneut rauszuwerfen</t>
         </is>
       </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -12644,6 +13884,11 @@
           <t>ICE verhaftet 22 Personen im Raum Chicago während eines dreitägigen Einsatzes</t>
         </is>
       </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -12693,6 +13938,11 @@
           <t>Bill Clinton: „Ich habe das Richtige getan“ während der Lewinsky-Affäre; „Ich schulde ihr keine Entschuldigung.“</t>
         </is>
       </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -12742,6 +13992,11 @@
           <t>Zwei Ebola-Fälle in der Demokratischen Republik Kongo bestätigt</t>
         </is>
       </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -12791,6 +14046,11 @@
           <t>Beweise zeigen, dass Papst Franziskus „Hauptakteur bei der Vertuschung“ des sexuellen Missbrauchs durch Geistliche in Chile ist: Experte</t>
         </is>
       </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -12840,6 +14100,11 @@
           <t>Hunderte Priester in Pennsylvania angeklagt, Begleitkirche in der Krise</t>
         </is>
       </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -12889,6 +14154,11 @@
           <t>Die American Jewish Historical Society veranstaltet die Veranstaltung „Zerstöre Israel“.</t>
         </is>
       </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -12938,6 +14208,11 @@
           <t>Trump droht mit der Entsendung von Militär, um die Flüchtlingskarawane aus Honduras zu blockieren</t>
         </is>
       </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -12987,6 +14262,11 @@
           <t>Brett Kavanaugh wird in einem vom FBI erhaltenen Brief beschuldigt, sich während seiner Schulzeit betrunken einer Frau aufgedrängt zu haben; Kavanaugh bestreitet, dass es passiert ist</t>
         </is>
       </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -13036,6 +14316,11 @@
           <t>Kavanaughs Nominierung explodiert vor Trumps Gesicht</t>
         </is>
       </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -13085,6 +14370,11 @@
           <t>Die Erholung nach dem Hurrikan in Puerto Rico wurde dadurch verschlimmert, dass fast eine Million Häuser illegal gebaut wurden</t>
         </is>
       </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -13134,6 +14424,11 @@
           <t>Der schwedische Premierminister schließt den Einsatz der Armee zur Beendigung der Bandengewalt nicht aus</t>
         </is>
       </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -13183,6 +14478,11 @@
           <t>Papst Franziskus gegen kontemplative Orden</t>
         </is>
       </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -13232,6 +14532,11 @@
           <t>Der Sicherheitsbeamte von Las Vegas, dem die Entdeckung des Schützen zugeschrieben wird, verschwand auf mysteriöse Weise in Luft</t>
         </is>
       </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -13281,6 +14586,11 @@
           <t>Texaner hinter 3D-gedruckten Waffen verspricht Rechtsstreit, während das Weiße Haus Gerichtsurteil unterstützt | Bangkok Post: Nachrichten</t>
         </is>
       </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -13330,6 +14640,11 @@
           <t>Bürgermeister von Sanctuary City schützte illegalen ausländischen mexikanischen Vergewaltiger</t>
         </is>
       </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -13379,6 +14694,11 @@
           <t>Der Rufmord an Richter Kavanaugh in letzter Minute</t>
         </is>
       </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -13428,6 +14748,11 @@
           <t>Munitionsverkäufer des Las-Vegas-Mörders unter Anklage des Bundes verhaftet</t>
         </is>
       </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -13477,6 +14802,11 @@
           <t>Brenda Snipes, Wahlleiterin im Broward County, tritt wegen Wahlbetrugs in Florida zurück</t>
         </is>
       </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -13526,6 +14856,11 @@
           <t>Hat der Bürgermeister von Oakland La Raza auf eine ICE-Razzia hingewiesen?</t>
         </is>
       </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -13575,6 +14910,11 @@
           <t>Das Weiße Haus stellt den Pass von CNN Acosta wieder her, führt jedoch strenge Verhaltensregeln ein</t>
         </is>
       </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -13624,6 +14964,11 @@
           <t>Das FBI verhaftet fünf Muslime aus dem Dschihad-Gelände in New Mexico, nur wenige Tage nachdem mehrere Anklagen fallengelassen wurden</t>
         </is>
       </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -13673,6 +15018,11 @@
           <t>Ungarns Ministerpräsident Viktor Orban verspricht, „gegen diejenigen zu kämpfen, die die christliche Identität Europas ändern wollen“</t>
         </is>
       </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -13722,6 +15072,11 @@
           <t>Barack Hussein Obama verheimlichte seine Bemühungen, dem Iran zu helfen</t>
         </is>
       </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -13771,6 +15126,11 @@
           <t>DOJ entsiegelt Anklage wegen Uranium-One-Skandal</t>
         </is>
       </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -13820,6 +15180,11 @@
           <t>Ein beliebter Bibelkurs an einer öffentlichen Schule in West Virginia steht vor einer rechtlichen Herausforderung</t>
         </is>
       </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -13869,6 +15234,11 @@
           <t>Neue Las-Vegas-Täter-Theorie: „Hätte gehetzt und unvorbereitet … hätte zu einem Unfall führen können, als würde er sich selbst in den Kopf schießen“</t>
         </is>
       </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -13918,6 +15288,11 @@
           <t>Trump ordnet die Freigabe von „Russian Probe“-Dokumenten, einschließlich Texten, an</t>
         </is>
       </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -13967,6 +15342,11 @@
           <t>11 Kinder wurden aus einem von muslimischen Extremisten betriebenen Gelände in New Mexico gerettet</t>
         </is>
       </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -14016,6 +15396,11 @@
           <t>Präsident Trump ordnet FBI-Ermittlungen gegen Kavanaugh nach einem Wutanfall der Demokraten an</t>
         </is>
       </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -14065,6 +15450,11 @@
           <t>Erzbischof Hebda und McCarricks Skandal</t>
         </is>
       </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -14114,6 +15504,11 @@
           <t>Trump begnadigt Viehzüchter aus Oregon, deren Inhaftierung den bewaffneten Konflikt im Jahr 2016 auslöste</t>
         </is>
       </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -14163,6 +15558,11 @@
           <t>Als die honduranische Karawane die Grenze erreicht, droht Trump mit der Entsendung des Militärs</t>
         </is>
       </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -14212,6 +15612,11 @@
           <t>Französische Behörden machen „Aufregung“ für Angriff durch Muslim verantwortlich, der „Allahu Akbar“ ruft</t>
         </is>
       </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -14261,6 +15666,11 @@
           <t>Liberale sind sich einig – Trump ist gegenüber Putin härter als Obama es war</t>
         </is>
       </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -14310,6 +15720,11 @@
           <t>Mann aus Virginia, der sich ISIS anschließen wollte, bekennt sich schuldig, über eine Auslandsreise gelogen zu haben</t>
         </is>
       </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -14359,6 +15774,11 @@
           <t>Dina Habib Powell: „Kein Interesse“ daran, Nikki Haley als UN-Botschafterin zu ersetzen</t>
         </is>
       </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -14408,6 +15828,11 @@
           <t>Die Jade-Helm-Verbindung der Obama-Ära zur aktuellen illegalen Einwanderungspolitik</t>
         </is>
       </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -14457,6 +15882,11 @@
           <t>Demokratenfreund Louis Farrakhan im Iran: „Tod für Amerika!“ – Amerika ist der „große Satan“</t>
         </is>
       </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -14506,6 +15936,11 @@
           <t>Der Informant von Uranium One bricht sein Schweigen: Moskau zahlte Millionen, um Hillary Clinton zu beeinflussen</t>
         </is>
       </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -14555,6 +15990,11 @@
           <t>Schweizer Bischof unterzeichnet Erklärung, in der er die Interpretation von Amoris Laetitia durch den Papst als „fremd“ gegenüber dem katholischen Glauben bezeichnet</t>
         </is>
       </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -14604,6 +16044,11 @@
           <t>Geert Wilders macht die politischen Eliten aufmerksam</t>
         </is>
       </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -14653,6 +16098,11 @@
           <t>Auf Video festgehalten: Gillum-Mitarbeiter macht rassistische Äußerungen und gibt zu, dass der Wahlkampf die Wähler belügt</t>
         </is>
       </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -14702,6 +16152,11 @@
           <t>Neues Filmmaterial vom Massaker in Las Vegas enthüllt mögliche Mündungsfeuer von Hubschraubern, die möglicherweise einen „Luftangriff“ durchgeführt haben</t>
         </is>
       </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -14751,6 +16206,11 @@
           <t>Deep State Insurrection widersetzt sich dem Befehl von POTUS Trump</t>
         </is>
       </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -14800,6 +16260,11 @@
           <t>Verschwörungstheoretiker beschlagnahmen einen Mann aus Mesa, der Munition an einen Attentäter in Las Vegas verkauft hat</t>
         </is>
       </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -14849,6 +16314,11 @@
           <t>Diese Fake-News-Story des Guardian beweist, dass man den Medien nicht trauen kann</t>
         </is>
       </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -14898,6 +16368,11 @@
           <t>Trumps Abenteuer mit Nordkorea endet mit einer „besonderen Bindung“ zu Kim</t>
         </is>
       </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -14947,6 +16422,11 @@
           <t>Islamisierung der Schulen: Der Fall West Virginia</t>
         </is>
       </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -14996,6 +16476,11 @@
           <t>Der Londoner Bezirk mit dem höchsten Anteil an Muslimen im Vereinigten Königreich stimmt für ein Einreiseverbot für Trump</t>
         </is>
       </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -15045,6 +16530,11 @@
           <t>Der jüngste Ebola-Ausbruch in der DR Kongo hat 17 Tote gefordert</t>
         </is>
       </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -15094,6 +16584,11 @@
           <t>Top-Polizist des Kongresses: Abgeordneter der demokratischen Fraktion im Repräsentantenhaus verschwand bei Ermittlungen zum muslimischen Spionagering</t>
         </is>
       </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -15143,6 +16638,11 @@
           <t>Mueller-Bericht: Keine weiteren Anklagen</t>
         </is>
       </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -15192,6 +16692,11 @@
           <t>Demokratische Kandidaten fordern, dass der vollständige Mueller-Bericht veröffentlicht wird</t>
         </is>
       </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -15241,6 +16746,11 @@
           <t>Demokraten im Kongress fordern, dass Barr den vollständigen Mueller-Bericht „ohne Verzögerung“ veröffentlicht</t>
         </is>
       </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -15290,6 +16800,11 @@
           <t>Mueller legt seinen Russland-Bericht dem Justizministerium vor</t>
         </is>
       </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -15339,6 +16854,11 @@
           <t>CNN reagiert auf Mueller News: „Riesiger Sieg für den Präsidenten“, Trump „bestätigt“</t>
         </is>
       </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -15388,6 +16908,11 @@
           <t>Trump fragte Freunde immer wieder, ob der Mueller-Bericht diese Woche fallen würde</t>
         </is>
       </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -15437,6 +16962,11 @@
           <t>Robert Mueller empfiehlt keine weiteren Anklagen</t>
         </is>
       </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -15486,6 +17016,11 @@
           <t>Kamala Harris fordert AG Barr auf, in der Mueller-Untersuchung auszusagen, während die Demokraten für 2020 den Berichtsrückgang aufgreifen</t>
         </is>
       </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -15535,6 +17070,11 @@
           <t>Berichte: Aus der Untersuchung des Sonderermittlers Robert Mueller werden keine neuen Anklagen hervorgehen</t>
         </is>
       </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -15584,6 +17124,11 @@
           <t>Sie beleidigen uns, Botschafter: Woody Johnson hat die besondere Beziehung eklatant missbraucht, sagt PETER OBORNE</t>
         </is>
       </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -15633,6 +17178,11 @@
           <t>Sowohl das britische Volk als auch die Politiker wollen den Brexit nicht</t>
         </is>
       </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -15682,6 +17232,11 @@
           <t>Keine Pause vom Brexit: RT wirft einen Blick auf die neuesten Entwicklungen, als Abgeordnete sagten: „Kein Urlaub für Sie“</t>
         </is>
       </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -15731,6 +17286,11 @@
           <t>Die USA reagieren mit Erleichterung und Skepsis auf das Ende der Mueller-Untersuchung</t>
         </is>
       </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -15780,6 +17340,11 @@
           <t>Adam Schiff droht, Mueller vorzuladen, nachdem die Russland-Ermittlungen abgeschlossen sind</t>
         </is>
       </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -15829,6 +17394,11 @@
           <t>Sadiq Khan wurde während des Feuerwerks wegen seiner Pro-EU-„Unterstützungsbotschaft“ kritisiert</t>
         </is>
       </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -15878,6 +17448,11 @@
           <t>Demokratischer Abgeordneter Lewis über den Post-Mueller-Bericht zum Amtsenthebungsverfahren gegen Trump: „Ich denke, dieser Tag wird kommen“</t>
         </is>
       </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -15927,6 +17502,11 @@
           <t>Ex-MI6-Chef sagt, Theresa Mays Brexit-Deal „bedroht die nationale Sicherheit“ und schadet den Beziehungen zu den USA</t>
         </is>
       </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -15976,6 +17556,11 @@
           <t>Großbritannien bittet die EU um eine Verlängerung der Brexit-Frist, um herauszufinden, was es tatsächlich will</t>
         </is>
       </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -16025,6 +17610,11 @@
           <t>Sind Mueller-Kritiker ihm jetzt eine Entschuldigung schuldig?</t>
         </is>
       </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -16074,6 +17664,11 @@
           <t>Die EU liebt britisches Geld mehr als die Demokratie</t>
         </is>
       </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -16123,6 +17718,11 @@
           <t>Theresa May droht bei der großen Brexit-Abstimmung eine katastrophale Niederlage, während Verbündete warnen: „Der Winter naht“</t>
         </is>
       </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -16172,6 +17772,11 @@
           <t>Außenminister Jeremy Hunt sagt, Großbritannien dürfe „seine Stärke“ nach dem Brexit nicht unterschätzen</t>
         </is>
       </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -16221,6 +17826,11 @@
           <t>Brexit in 23 Tagen: EU sagt immer noch „keine Lösung“</t>
         </is>
       </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -16270,6 +17880,11 @@
           <t>Gewerkschaftsaktivisten „könnten wegen Corbyns Haltung zum Brexit-Referendum aus der Partei austreten“</t>
         </is>
       </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -16319,6 +17934,11 @@
           <t>„Altmodische Politik weggeworfen“: Sieben Labour-Abgeordnete treten wegen Brexit und „Antisemitismus“ aus der Partei aus</t>
         </is>
       </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -16368,6 +17988,11 @@
           <t>Tom Steyer versammelt Unterstützer nach Abschluss des Mueller-Berichts</t>
         </is>
       </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -16417,6 +18042,11 @@
           <t>Muellers Ermittlungen dauerten 674 Tage.</t>
         </is>
       </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -16466,6 +18096,11 @@
           <t>Die Polizei bereitet sich auf den Einsatz in Nordirland für den Fall eines No-Deal-Brexit vor</t>
         </is>
       </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -16515,6 +18150,11 @@
           <t>Mueller-Bericht: „Die USA haben die EU gezwungen, ihre Sanktionen ohne Beweise durchzusetzen“</t>
         </is>
       </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -16564,6 +18204,11 @@
           <t>Zuversichtlicher Trump und besorgtes Washington warten auf AG Barrs Bericht über Muellers wichtigste Erkenntnisse</t>
         </is>
       </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -16613,6 +18258,11 @@
           <t>Der Mueller-Bericht wird endlich fallen gelassen, die Demokraten bereiten eine Liste mit Forderungen vor</t>
         </is>
       </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -16662,6 +18312,11 @@
           <t>Die britische Regierung führt mit 150 Lastwagen eine Generalprobe für einen No-Deal-Brexit durch</t>
         </is>
       </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -16711,6 +18366,11 @@
           <t>Der britische Premierminister warnt vor „Neuland“, wenn der Brexit-Deal abgelehnt wird</t>
         </is>
       </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -16760,6 +18420,11 @@
           <t>Trump sieht sich mit Mueller-Bericht in der Mar-a-Lago-Blase konfrontiert</t>
         </is>
       </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -16809,6 +18474,11 @@
           <t>Die Mehrheit der Tory-Wähler möchte, dass ihre Abgeordneten den Deal von Theresa May unterstützen</t>
         </is>
       </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -16858,6 +18528,11 @@
           <t>Mueller-Bericht über Präsident Trump an Generalstaatsanwalt geschickt</t>
         </is>
       </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -16907,6 +18582,11 @@
           <t>Mueller verstehen: Was Sie über den Bericht zur Russland-Untersuchung wissen müssen</t>
         </is>
       </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -16956,6 +18636,11 @@
           <t>Die britische „Gelbweste“, die einen EU-freundlichen Abgeordneten als Nazi bezeichnete, wird von der Polizei festgenommen</t>
         </is>
       </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -17005,6 +18690,11 @@
           <t>ENTHÜLLT: Anti-Brexit-Marsch ein Drittel der von den Organisatoren behaupteten Größe</t>
         </is>
       </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -17054,6 +18744,11 @@
           <t>Beto O'Rourke sagt, er glaube immer noch, dass Trump mit Russland konspiriert habe</t>
         </is>
       </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -17103,6 +18798,11 @@
           <t>Abgeordnete drohen mit Regierungsstillstand, um No-Deal-Brexit zu verhindern</t>
         </is>
       </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -17152,6 +18852,11 @@
           <t>Rückblende: Howard Dean sagt fälschlicherweise voraus, dass Mueller Jared Kushner anklagen wird</t>
         </is>
       </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -17201,6 +18906,11 @@
           <t>Die Demokraten von 2020 fordern die Veröffentlichung des Mueller-Berichts</t>
         </is>
       </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -17250,6 +18960,11 @@
           <t>Bericht: Theresa May könnte die endgültige Abstimmung über das Brexit-Abkommen erneut verschieben</t>
         </is>
       </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -17299,6 +19014,11 @@
           <t>Delingpole: Eine weitere Kamikaze-Verschwörung der Abgeordneten, den Brexit mit einem Shutdown im Trump-Stil zu zerstören</t>
         </is>
       </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -17348,6 +19068,11 @@
           <t>Jerome Corsi, Mitarbeiter von Roger Stone, feiert das Ende der Mueller-Untersuchung, nachdem er sich geweigert hat, einen Plädoyervertrag zu unterzeichnen</t>
         </is>
       </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -17397,6 +19122,11 @@
           <t>Adam Schiff weist Berichte zurück, dass die Anklagen gegen Mueller abgeschlossen seien</t>
         </is>
       </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -17446,6 +19176,11 @@
           <t>Was passiert, wenn niemand ins Gefängnis geht?</t>
         </is>
       </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -17495,6 +19230,11 @@
           <t>Mueller ist fertig, aber die Trump-Ermittlungen nehmen nur noch Fahrt auf</t>
         </is>
       </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -17544,6 +19284,11 @@
           <t>Kabelzuschauer verdauen Mueller-Nachrichten durch Hannity, Maddow</t>
         </is>
       </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -17593,6 +19338,11 @@
           <t>Der „Brexit-Plan B“ von Premierministerin May ähnelt stark dem „Brexit-Plan A“</t>
         </is>
       </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -17642,6 +19392,11 @@
           <t>Der Brite Gavin Williamson macht Russland und China aufmerksam, das ist kein Scherz</t>
         </is>
       </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -17691,6 +19446,11 @@
           <t>Trump und Melania strahlen, als sie in Mar-a-Lago mit Führern karibischer Staaten für Fotos posieren</t>
         </is>
       </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -17740,6 +19500,11 @@
           <t>Schiff über Ende der Mueller-Untersuchung: „Wir müssen die Wahrheit herausfinden“</t>
         </is>
       </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -17789,6 +19554,11 @@
           <t>Hirono: Mueller-Bericht „Ende vom Anfang“ – In anderen Untersuchungen „kommt noch mehr“</t>
         </is>
       </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -17838,6 +19608,11 @@
           <t>Der britische Generalstaatsanwalt verstößt gegen Mays überarbeiteten Brexit-Deal</t>
         </is>
       </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -17887,6 +19662,11 @@
           <t>Theresa May hat nicht die Stimmen</t>
         </is>
       </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -17936,6 +19716,11 @@
           <t>Don Trump Jr. nutzt das Vaterschafts-Mem von Maury Povich, um sich über die Demokraten lustig zu machen</t>
         </is>
       </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -17985,6 +19770,11 @@
           <t>Sieben britische Arbeitsgesetzgeber sind wegen Jeremy Corbyns Umgang mit Brexit und Antisemitismus zurückgetreten</t>
         </is>
       </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -18034,6 +19824,11 @@
           <t>Regierung schürt „apokalyptische Ängste“ wegen eines klaren Austritts aus der EU</t>
         </is>
       </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -18083,6 +19878,11 @@
           <t>EU profitiert vom Handel mit Großbritannien, während London Geld verliert – politischer Aktivist</t>
         </is>
       </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -18132,6 +19932,11 @@
           <t>Mueller-Bericht wird am Samstag von A.G. Barr geprüft</t>
         </is>
       </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -18181,6 +19986,11 @@
           <t>Die norwegische Regierung schlägt ein Gesetz vor, um die Rechte der Bürger im Falle eines No-Deal-Brexit zu sichern</t>
         </is>
       </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -18230,6 +20040,11 @@
           <t>„Treten Sie Farages neuer Partei bei“: Tory-Minister schlägt auf Rees-Moggs „verräterische“ Brexit-Befürworter ein</t>
         </is>
       </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -18279,6 +20094,11 @@
           <t>Der britische Labour-Chef Corbyn verliert an Unterstützung, weil er sich nicht zur zweiten Brexit-Abstimmung geäußert hat</t>
         </is>
       </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -18328,6 +20148,11 @@
           <t>Trump-Berater optimistisch: Mueller „hat nicht das Zeug dazu“</t>
         </is>
       </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -18377,6 +20202,11 @@
           <t>Theresa May unterlag erneut, während die britische „Shitshow“ damit drohte, den Brexit zu blockieren</t>
         </is>
       </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -18426,6 +20256,11 @@
           <t>Schrecklicher Brexit-Deal: Alle EU-Staaten könnten Großbritannien um Handelszugeständnisse bitten - Prof</t>
         </is>
       </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -18475,6 +20310,11 @@
           <t>Die Brexit-Abstimmung wird „definitiv“ stattfinden, sagt die britische Premierministerin May, da neue Umfragen zeigen, dass die meisten Briten jetzt für den Verbleib stimmen würden</t>
         </is>
       </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -18524,6 +20364,11 @@
           <t>„Wunschdenken“: Tory-Abgeordnete weisen Mays Hoffnungen auf eine Änderung ihrer Meinung zum Brexit-Deal zurück</t>
         </is>
       </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -18573,6 +20418,11 @@
           <t>Mueller schließt Russland-Trump-Untersuchung ab; Der Gesetzgeber fordert eine sofortige Freilassung</t>
         </is>
       </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -18622,6 +20472,11 @@
           <t>RICHARD LITTLEJOHN: In der Hauptstadt kommt es zum ersten Mal in diesem Jahr zu Messerstechereien</t>
         </is>
       </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -18671,6 +20526,11 @@
           <t>Russland. Energiesanktionen richten sich gegen die Europäer</t>
         </is>
       </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -18720,6 +20580,11 @@
           <t>Ukraine/Europäische Union: Auf dem Weg zum europäischen geopolitischen Selbstmord</t>
         </is>
       </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -18769,6 +20634,11 @@
           <t>Die Krise der Gasinflation ist noch lange nicht vorbei – Wo bleiben die Preise endlich stehen?</t>
         </is>
       </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -18818,6 +20688,11 @@
           <t>Das Vereinigte Königreich hat den Start eines neuen Ausbildungsprogramms für Tausende ukrainischer Soldaten auf seinem Boden bestätigt, das voraussichtlich mindestens mehrere Wochen für jede Rekrutengruppe dauern wird.</t>
         </is>
       </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -18867,6 +20742,11 @@
           <t>Wie lange werden die hohen Preise an der Zapfsäule anhalten? „So lange es dauert“, so Biden</t>
         </is>
       </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -18916,6 +20796,11 @@
           <t>Einwanderung: Integration wird durch Diskriminierung behindert</t>
         </is>
       </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -18965,6 +20850,11 @@
           <t>Wladimir Putin war gezwungen, sich an einen Autokraten zu wenden, der größer war als er</t>
         </is>
       </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -19014,6 +20904,11 @@
           <t>Covid: Die Pandemie verursacht laut WHO 13 bis 17 Millionen Todesfälle</t>
         </is>
       </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -19063,6 +20958,11 @@
           <t>Wurde eine Anti-Abtreibungskonferenz von einem RN-Abgeordneten in der Nationalversammlung organisiert?</t>
         </is>
       </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -19112,6 +21012,11 @@
           <t>Macron ist mit seiner Steuerschikane der Feind Frankreichs und der Franzosen</t>
         </is>
       </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -19161,6 +21066,11 @@
           <t>Angesichts des gesetzlosen Lügners kämpfte Marine gut</t>
         </is>
       </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -19210,6 +21120,11 @@
           <t>Franziskus, Papst der Armen und der Ökologie? Oder Papst der globalen Elite?</t>
         </is>
       </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -19259,6 +21174,11 @@
           <t>Joe Biden und die G-7 wollen Milliarden von Dollar ausgeben, um „grüne Projekte“ in der Dritten Welt zu finanzieren</t>
         </is>
       </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -19308,6 +21228,11 @@
           <t>Macron will die Ungeimpften „verärgern“: eine erschreckende totalitäre Wende</t>
         </is>
       </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -19357,6 +21282,11 @@
           <t>Wird Russland zu einer Kriegsstrategie übergehen?</t>
         </is>
       </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -19406,6 +21336,11 @@
           <t>Warum Indien der Verfechter des Krieges in der Ukraine ist</t>
         </is>
       </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -19455,6 +21390,11 @@
           <t>Coronavirus: Bolsonaro droht seinerseits mit Austritt aus der WHO</t>
         </is>
       </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -19504,6 +21444,11 @@
           <t>SCHOCKIERENDE Anschuldigungen aus Moskau! Westliche Pharmariesen, gemeinnützige Organisationen und sogar die Amerikanische Demokratische Partei waren an dem ukrainischen Biolaborprojekt beteiligt!</t>
         </is>
       </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -19553,6 +21498,11 @@
           <t>Öffne deine Augen! Die NATO, diese antieuropäische Struktur…</t>
         </is>
       </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -19602,6 +21552,11 @@
           <t>Taiwan: Xi Jinping fordert Joe Biden auf, nicht „mit dem Feuer zu spielen“</t>
         </is>
       </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -19651,6 +21606,11 @@
           <t>Angriff auf das Kapitol: Letztlich war Trump nicht lustig</t>
         </is>
       </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -19700,6 +21660,11 @@
           <t>Krieg in der Ukraine: Selenskyj wirft Amnesty International vor, „versucht zu haben, dem Terrorstaat Russland Amnestie zu gewähren“.</t>
         </is>
       </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -19749,6 +21714,11 @@
           <t>Nach dem Recht auf Abtreibung will Texas Frauen verbieten</t>
         </is>
       </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -19798,6 +21768,11 @@
           <t>Nach Erhalt der Atomwaffen wird die Ukraine zusammen mit Polen und ganz Europa verschwinden</t>
         </is>
       </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -19847,6 +21822,11 @@
           <t>Ungarn erklärt der Europäischen Union den Krieg: „Niemand wird ein Embargo gegen russisches Gas verhängen“</t>
         </is>
       </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -19896,6 +21876,11 @@
           <t>Ende der Umweltbürokratie in den USA, aber nicht in der EU</t>
         </is>
       </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -19945,6 +21930,11 @@
           <t>Macron/Putin: Welche Botschaft wird übermittelt?</t>
         </is>
       </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -19994,6 +21984,11 @@
           <t>Zentralbanken kontrollieren die Inflation nicht</t>
         </is>
       </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -20043,6 +22038,11 @@
           <t>Vereinigte Staaten: Die Demokraten bereiten ihren eigenen Aufstand vor</t>
         </is>
       </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -20092,6 +22092,11 @@
           <t>Wolodymyr Selenskyj will Wladimir Putin treffen, um „den Krieg zu beenden“</t>
         </is>
       </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -20141,6 +22146,11 @@
           <t>Was die Ukraine und China angeht, ist die Europäische Union ein atlantischer und verantwortungsloser Lakai</t>
         </is>
       </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -20190,6 +22200,11 @@
           <t>Ukraine: Blinken wird zwei Monate nach Kriegsbeginn in Kiew erwartet</t>
         </is>
       </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -20239,6 +22254,11 @@
           <t>Unterstützen westliche Spione die neuen „ukrainischen Weißhelme“?</t>
         </is>
       </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -20288,6 +22308,11 @@
           <t>Emmanuel Macron wurde zum Garanten der republikanischen Front gegen die extreme Rechte. Fünf Jahre später ist der RN stärker als je zuvor. Deshalb wenden sich die Regierung und die LREM-Abgeordneten an ihn. Alle Schande, betrunken.</t>
         </is>
       </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -20337,6 +22362,11 @@
           <t>Nein, Veganismus wird nicht die Welt retten, aber es könnte Ihrer Gesundheit schaden</t>
         </is>
       </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -20386,6 +22416,11 @@
           <t>Von der EU des Friedens zur EU des Krieges und dann zu ihrer Verflüssigung?</t>
         </is>
       </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -20435,6 +22470,11 @@
           <t>Ukraine – Russische Rakete, die auf Zivilisten zielt, tötet versehentlich mehrere ukrainische Soldaten</t>
         </is>
       </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -20484,6 +22524,11 @@
           <t>Biden nennt MAGA-Ideologie „extrem“</t>
         </is>
       </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -20533,6 +22578,11 @@
           <t>Fauci gibt zu, dass „Sperren eine Möglichkeit sind, Menschen impfen zu lassen“</t>
         </is>
       </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -20582,6 +22632,11 @@
           <t>China setzt Militärübungen in der Nähe von Taiwan fort</t>
         </is>
       </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -20631,6 +22686,11 @@
           <t>Die EU verhängt Sanktionen gegen den ehemaligen ukrainischen Präsidenten Viktor Janukowitsch</t>
         </is>
       </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -20680,6 +22740,11 @@
           <t>Pelosi in Taiwan: Nationalistische Chinesen kritisieren die „zu zaghafte“ Reaktion ihrer Regierung</t>
         </is>
       </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -20729,6 +22794,11 @@
           <t>Gesundheitskrise oder Demokratiekrise</t>
         </is>
       </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -20778,6 +22848,11 @@
           <t>Ist Biden für die Weltsicherheit gefährlicher als Trump?</t>
         </is>
       </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -20827,6 +22902,11 @@
           <t>Statt glücklicher Globalisierung die Ausweitung der Knappheit</t>
         </is>
       </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -20876,6 +22956,11 @@
           <t>Impfpolitik: Spanien wird vernünftig, Frankreich bleibt bestehen</t>
         </is>
       </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -20925,6 +23010,11 @@
           <t>Präsidentschaftswahl 2022: Das europäische Embargo gegen russisches Öl nach der Wahl verschoben, um Marine Le Pen nicht zu begünstigen?</t>
         </is>
       </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -20974,6 +23064,11 @@
           <t>Das Duo Macron-Putin, zwischen Machtgleichgewicht und Pragmatismus</t>
         </is>
       </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -21023,6 +23118,11 @@
           <t>„Macron geht unter“: Mélenchon reagiert auf die Erklärung des Präsidenten</t>
         </is>
       </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -21072,6 +23172,11 @@
           <t>Die NATO und Russland tun so, als hätten sie keine Angst</t>
         </is>
       </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -21121,6 +23226,11 @@
           <t>Schweizer Neutralität: Kollateralschaden durch den Krieg in der Ukraine</t>
         </is>
       </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -21170,6 +23280,11 @@
           <t>Kampf gegen Covid: Lösungen werden vor Ort kommen</t>
         </is>
       </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -21219,6 +23334,11 @@
           <t>Russland hilft Donbass, Frankreich militarisiert die Ukraine</t>
         </is>
       </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -21268,6 +23388,11 @@
           <t>Hören wir mit der Gesundheitspanik auf und machen wir uns an die Arbeit</t>
         </is>
       </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -21317,6 +23442,11 @@
           <t>Russisches Staatsfernsehen beruhigt Zuschauer vor Atomkrieg: „Eines Tages werden wir alle sterben“</t>
         </is>
       </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -21366,6 +23496,11 @@
           <t>In Italien bedroht eine historische Dürre die Landwirtschaft</t>
         </is>
       </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -21415,6 +23550,11 @@
           <t>Hut ab vor Israel: 2 palästinensische Terroristen getötet und 19 weitere verletzt!</t>
         </is>
       </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -21464,6 +23604,11 @@
           <t>Das Verteidigungsministerium der Russischen Föderation veröffentlichte Daten über die Arbeit mit Zeckeninfektionen in biologischen Labors der Vereinigten Staaten in der Ukraine</t>
         </is>
       </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -21513,6 +23658,11 @@
           <t>Das Verteidigungsministerium der Russischen Föderation: In Avdeevka halten die Streitkräfte der Ukraine Zivilisten in einer Kokerei fest</t>
         </is>
       </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -21562,6 +23712,11 @@
           <t>Ukrainische Soldaten dienen als Laborratten? Russland behauptet, in den befreiten Gebieten des Donbass zwei weitere amerikanische militärische Biolabore gefunden zu haben.</t>
         </is>
       </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -21611,6 +23766,11 @@
           <t>Donald Trump zu Eric Zemmour: „Macron ist ein netter Kerl“</t>
         </is>
       </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -21660,6 +23820,11 @@
           <t>Trump/Clinton 2016, Le Pen/Macron 2022, Gemeinsamkeiten, Unterschiede</t>
         </is>
       </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -21709,6 +23874,11 @@
           <t>Trump: Putin „sollte alle Informationen über Hunter Biden veröffentlichen“.</t>
         </is>
       </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -21758,6 +23928,11 @@
           <t>Was wäre, wenn Frankreich Amerikanern, die eine Abtreibung wünschen, Asyl anbieten würde?</t>
         </is>
       </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -21807,6 +23982,11 @@
           <t>Totalitarismus in vollem Gange: In Spanien könnten Abtreibungsgegner wegen „Belästigung“ zu Gefängnisstrafen verurteilt werden</t>
         </is>
       </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -21856,6 +24036,11 @@
           <t>[Ukraine] Warum ist Russland nicht vom Rest der Welt isoliert?</t>
         </is>
       </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -21905,6 +24090,11 @@
           <t>Superprofite: Bruno Le Maire wird vom Abgeordneten RN Tanguy wie ein Pflaumenbaum geschüttelt</t>
         </is>
       </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -21954,6 +24144,11 @@
           <t>Krieg ist Krieg, und dieser Krieg wird sich verschärfen.</t>
         </is>
       </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -22003,6 +24198,11 @@
           <t>Wirtschaft: In Frankreich und der EU läuft nichts gut!</t>
         </is>
       </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -22052,6 +24252,11 @@
           <t>Für Joe Biden ist Wladimir Putin ein „Schlächter“ und ein „Diktator“</t>
         </is>
       </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -22101,6 +24306,11 @@
           <t>„Wir werden das Problem der Unsicherheit nicht lösen, bis wir uns mit dem Problem der Einwanderung befassen“</t>
         </is>
       </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -22150,6 +24360,11 @@
           <t>Die Ukraine erklärt der Opposition den Krieg: eine gewisse Vision von „Demokratie“</t>
         </is>
       </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -22199,6 +24414,11 @@
           <t>Joe Biden und die saudischen Despoten: ein sehr aufschlussreicher Vortrag</t>
         </is>
       </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -22248,6 +24468,11 @@
           <t>Borrel: Die G20-Staaten teilen in der Ukraine-Frage nicht die Position der EU und der G7</t>
         </is>
       </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -22297,6 +24522,11 @@
           <t>RaHDIt-Hacker wirft den USA vor, Kiew Satellitenbilder zur Verfügung zu stellen, um Russland zu bombardieren</t>
         </is>
       </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -22346,6 +24576,11 @@
           <t>Recht auf Abtreibung in den USA bedroht: Wirf ihnen den Stock zurück ins Gesicht</t>
         </is>
       </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -22395,6 +24630,11 @@
           <t>G7: Ukraine, Klima, Ernährungsunsicherheit ... Woran Sie sich bei den Gipfelankündigungen erinnern sollten</t>
         </is>
       </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -22444,6 +24684,11 @@
           <t>In Frankreich wird eine Abtreibung ohne Zittern garantiert</t>
         </is>
       </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -22493,6 +24738,11 @@
           <t>Mit „MBS“ sprach Macron über die Ukraine, Energie, Terrorismus, Israel-Palästina … und ein wenig Menschenrechte</t>
         </is>
       </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -22542,6 +24792,11 @@
           <t>Dank des Rabatts an der Zapfsäule dürfte die Inflation zu Beginn des Schuljahres nachlassen</t>
         </is>
       </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -22591,6 +24846,11 @@
           <t>Umfrage: Die Franzosen halten rassistische Äußerungen ab 75 für akzeptabel</t>
         </is>
       </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -22640,6 +24900,11 @@
           <t>Emmanuel Macron wird sich mit der globalen Erwärmung befassen und ihn auffordern, seine Aggression sofort einzustellen</t>
         </is>
       </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -22689,6 +24954,11 @@
           <t>Informationskrieg: Polnische Regierung startet #StopRussiaNow</t>
         </is>
       </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -22738,6 +25008,11 @@
           <t>Notfallausgabe von VACCINE ALERT</t>
         </is>
       </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -22787,6 +25062,11 @@
           <t>„Rechtsextremer Antisemit“: Warschau ruft französischen Botschafter nach Macrons Äußerungen über den polnischen Premierminister ein</t>
         </is>
       </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -22836,6 +25116,11 @@
           <t>Moldawien riskiert den Verlust seiner Unabhängigkeit aufgrund westlicher Turniere – Ex-Präsident Dodon</t>
         </is>
       </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -22885,6 +25170,11 @@
           <t>„Konferenz zur Zukunft Europas: ein Simulakrum der partizipativen Demokratie?“</t>
         </is>
       </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -22934,6 +25224,11 @@
           <t>Aus Texas fordert Viktor Orban die amerikanischen Konservativen auf, angesichts des von der Linken geführten „Kulturkrieges“ „ihre Kräfte zu bündeln“.</t>
         </is>
       </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -22983,6 +25278,11 @@
           <t>Grüner Kapitalismus: eine weitere Unternehmensfalle</t>
         </is>
       </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -23032,6 +25332,11 @@
           <t>Vote Marine, um Macrons Impfpolitik ein Ende zu setzen</t>
         </is>
       </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -23081,6 +25386,11 @@
           <t>Emmanuel Macron kündigt an, dass der Impfpass für den Zugang zu Impfzentren obligatorisch wird</t>
         </is>
       </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -23130,6 +25440,11 @@
           <t>Für einen rassistischen Ansatz zur Einwanderung</t>
         </is>
       </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -23179,6 +25494,11 @@
           <t>Wladimir Putin schickt seine Armee in den Mittelpunkt der Erde, um „die Lava zu entnazifizieren“</t>
         </is>
       </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -23228,6 +25548,11 @@
           <t>Wie Macron und seine Clique die Arbeitslosenzahlen manipulieren</t>
         </is>
       </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -23277,6 +25602,11 @@
           <t>Johnson warnt Macron davor, jetzt eine Lösung für die Ukraine zu versuchen – POLITICO</t>
         </is>
       </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -23326,6 +25656,11 @@
           <t>Nächsten Sonntag werden Sie für Frieden oder Krieg stimmen!</t>
         </is>
       </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -23375,6 +25710,11 @@
           <t>Russland werde den Ausbruch eines Dritten Weltkriegs nicht zulassen, sagt Medwedew</t>
         </is>
       </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -23424,6 +25764,11 @@
           <t>„Die Klimastrategie der Europäischen Union soll die Entwaldung weltweit verstärken“</t>
         </is>
       </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -23473,6 +25818,11 @@
           <t>Covid-Varianten: Neustart oder saisonales Virus?</t>
         </is>
       </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -23522,6 +25872,11 @@
           <t>Alle gesundheitspolitischen Entscheidungen von Emmanuel Macron haben mehr als 600 Milliarden gekostet, für welches Ergebnis?</t>
         </is>
       </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -23571,6 +25926,11 @@
           <t>Laut einer Entscheidung des Obersten Gerichtshofs der Vereinigten Staaten sind alle geimpften Menschen auf der ganzen Welt „Transhumanisten“.</t>
         </is>
       </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -23620,6 +25980,11 @@
           <t>Ukraine-Krieg: Der tückische Wunsch, Gutes zu tun und zwar gleich</t>
         </is>
       </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -23669,6 +26034,11 @@
           <t>"Geht Richtung Ende der Pandemie" – Virologe Stöhr zu Omikron-Verläufen</t>
         </is>
       </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -23718,6 +26088,11 @@
           <t>Putin und George W. Bush: Fake-Cowboys mit False Flags und brutalen Kriegen</t>
         </is>
       </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -23767,6 +26142,11 @@
           <t>„Die westliche Propaganda ist gescheitert“! Russland zieht Truppen von Grenze ab, nachdem Medien sagten, dass eine Invasion unmittelbar bevorstehe</t>
         </is>
       </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -23816,6 +26196,11 @@
           <t>Der nächste Krieg wird ums Wasser geführt – Wer Wasser hat, hat Macht – und wer den Zugang zu den Quellen hat, hat noch mehr Macht</t>
         </is>
       </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -23865,6 +26250,11 @@
           <t>Klimawandel: Wie der „Spiegel“ zu linker Gewalt aufruft</t>
         </is>
       </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -23914,6 +26304,11 @@
           <t>G7-Außenminister trommeln für den selbstzerstörerischen Krieg gegen Russland</t>
         </is>
       </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -23963,6 +26358,11 @@
           <t>Planspiel: Ausbruch von Affenpocken kam wie erwartet</t>
         </is>
       </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -24012,6 +26412,11 @@
           <t>AfD: Allein in Hamburg: Eine halbe Milliarde Euro für die Gesundheitsversorgung von Asylbewerbern!</t>
         </is>
       </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -24061,6 +26466,11 @@
           <t>Das neue Wahrheitsministerium des Biden-Regimes, auch bekannt als „Desinformationsbehörde“ des Ministeriums für Innere Sicherheit (DHS), ist nichts anderes als verkleideter Autoritarismus.</t>
         </is>
       </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -24110,6 +26520,11 @@
           <t>WHO-Impfkampagne mit fatalen Folgen: Immer mehr Fälle von „Impf-Polio” in Afrika</t>
         </is>
       </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -24159,6 +26574,11 @@
           <t>Warnung vor Weltkrieg: Papst kritisiert NATO-Osterweiterung als Provokation</t>
         </is>
       </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -24208,6 +26628,11 @@
           <t>Zwei Studien zeigen, dass das zirkulierende Affenpockenvirus in einem Biolabor manipuliert wurde</t>
         </is>
       </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -24257,6 +26682,11 @@
           <t>Nächster Inflationsschock! Ein Euro kostet jetzt 117 Cent</t>
         </is>
       </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -24306,6 +26736,11 @@
           <t>Kämpfst du noch? Die neue Kriegs-Rhetorik der Medien</t>
         </is>
       </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -24355,6 +26790,11 @@
           <t>Stationen dicht: Krankenhäuser sorgen sich wegen vieler Ausfälle durch Corona</t>
         </is>
       </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -24404,6 +26844,11 @@
           <t>Präsident Putins Einsicht in die staatliche Souveränität ist lehrreich für alle Länder</t>
         </is>
       </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -24453,6 +26898,11 @@
           <t>Eine neue Kirche, ein neuer Glauben, ein neues Volk</t>
         </is>
       </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -24502,6 +26952,11 @@
           <t>Die große Impfstoffkatastrophe</t>
         </is>
       </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -24551,6 +27006,11 @@
           <t>Supreme Court: Demokraten haben Macht der Abtreibungsgegner unterschätzt</t>
         </is>
       </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -24600,6 +27060,11 @@
           <t>Madrid: Präsident Erdoğan hat den NATO-Gipfel reich beschenkt verlassen</t>
         </is>
       </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -24649,6 +27114,11 @@
           <t>Lösung für Personalmangel an Flughäfen: Festsitzende Urlauber sollen einspringen, weil sie eh gerade Zeit haben</t>
         </is>
       </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -24698,6 +27168,11 @@
           <t>Die neuen Inflationsregeln kommen</t>
         </is>
       </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -24747,6 +27222,11 @@
           <t>SBU bereitet zynische Provokation mit Leichen vor, um Russland der Kriegsverbrechen zu beschuldigen</t>
         </is>
       </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -24796,6 +27276,11 @@
           <t>Poroschenko: Minsker Abkommen II diente dazu, Zeit zu gewinnen</t>
         </is>
       </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -24845,6 +27330,11 @@
           <t>Henry Kissinger: „Es gibt drei mögliche Ausgänge dieses Krieges“</t>
         </is>
       </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -24894,6 +27384,11 @@
           <t>Mehr COVID-19-Todesfälle bei Kindern seit Impfbeginn – und niemand erforscht den Grund</t>
         </is>
       </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -24943,6 +27438,11 @@
           <t>Impfzwang bei Lufthansa verursacht Luftfahrt Chaos</t>
         </is>
       </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -24992,6 +27492,11 @@
           <t>"Gas gibt es gar nicht. Es ist eine Erfindung der Regierung" – Querheizer sieht Winter entspannt entgegen</t>
         </is>
       </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -25041,6 +27546,11 @@
           <t>Sonneborn-Appell: Diesen Hinweis gibt der PARTEI-Chef zur OB-Wahl in Dresden</t>
         </is>
       </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -25090,6 +27600,11 @@
           <t>Sonntagsfrage: Was halten Sie davon, dass sich Lindner während der Koalitionsverhandlungen mit Porsche abgesprochen haben soll?</t>
         </is>
       </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -25139,6 +27654,11 @@
           <t>Lawrow: "Wir wollen die ukrainische Regierung auswechs… wie bitte? Das passiert alle 5 Jahre automatisch durch eine Wahl? Warum macht man denn sowas?"</t>
         </is>
       </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -25188,6 +27708,11 @@
           <t>US-COVID19-Todesfälle brechen die 1 Millionen-Marke!</t>
         </is>
       </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -25237,6 +27762,11 @@
           <t>Eine neue demokratisch-souveränistische Bewegung formiert sich in Italien</t>
         </is>
       </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -25286,6 +27816,11 @@
           <t>EU-Chefdiplomat beklagt sich über mangelnden Rückhalt für antirussischen Kurs durch Globalen Süden</t>
         </is>
       </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -25335,6 +27870,11 @@
           <t>Ist es Magie? Maßnahmengegner und -befürworter sehen sich von Corona-Expertenrat komplett bestätigt</t>
         </is>
       </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -25384,6 +27924,11 @@
           <t>Wer archaische Traditionen zu unserem Alltag machen will, hat Deutschland zu verlassen!</t>
         </is>
       </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -25433,6 +27978,11 @@
           <t>NATO gestärkt, Russland geschwächt: Ist Putin ein Agent des Westens?</t>
         </is>
       </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -25482,6 +28032,11 @@
           <t>„Die Nato ist nicht aggressiv“: Scholz stellt Russlands Nato-Sicherheitsbedenken in Frage</t>
         </is>
       </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -25531,6 +28086,11 @@
           <t>Endlich mit dem Virus leben lernen</t>
         </is>
       </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -25580,6 +28140,11 @@
           <t>Russische Truppen simulieren einen Atomangriff nahe Königsberg</t>
         </is>
       </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -25629,6 +28194,11 @@
           <t>Neue Pipeline: Türkei und Israel wollen Europa von Putin-Gas befreien</t>
         </is>
       </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -25678,6 +28248,11 @@
           <t>Auf Telefonstreich reingefallen: Ex-US-Präsident Bush bestätigt die Existenz der US-Biolabore in der Ukraine</t>
         </is>
       </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -25727,6 +28302,11 @@
           <t>NATO gegen Russland: Was passiert als Nächstes?</t>
         </is>
       </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -25776,6 +28356,11 @@
           <t>Die Nato allein zuhaus</t>
         </is>
       </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -25825,6 +28410,11 @@
           <t>Geheimer NATO-Bericht via Wikileaks zeigte miserable russische Streitkräfte, Drang zu taktischen Atomwaffen</t>
         </is>
       </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -25874,6 +28464,11 @@
           <t>Erzbischof Viganò: Herrscher wollen Auslöschung der Völker!</t>
         </is>
       </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -25923,6 +28518,11 @@
           <t>Bis 380 US-Dollar pro Barrel: Experten warnen von dramatischen Erdölpreissteigerungen</t>
         </is>
       </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -25972,6 +28572,11 @@
           <t>Und wenn wir vor die Hunde gehen: Hauptsache Russland gewinnt nicht</t>
         </is>
       </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -26021,6 +28626,11 @@
           <t>Russland spürt die Auswirkungen westlicher Sanktionen, aber sie sind alles andere als unerträglich</t>
         </is>
       </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -26070,6 +28680,11 @@
           <t>Fossile Industrie, Rüstung, Geheimdienst</t>
         </is>
       </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -26119,6 +28734,11 @@
           <t>Ambivalenz gegenüber dem Putin-Regime und dem ukrainischen Widerstand</t>
         </is>
       </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -26168,6 +28788,11 @@
           <t>Aggressive Landnahme &amp; lauter „Einzelfälle“: Kampf der Kulturen</t>
         </is>
       </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -26217,6 +28842,11 @@
           <t>Italienischer Ärzte-Chef: Ansteckungen trotz Impfung, Grüner Pass ist sinnlos</t>
         </is>
       </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -26266,6 +28896,11 @@
           <t>Religiöse Führer sagen, dass Covid-Impfungen für den Anstieg von „dämonischen Besessenheit“ verantwortlich ist</t>
         </is>
       </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -26315,6 +28950,11 @@
           <t>Wirtschaftsgipfel in Sankt Petersburg: Putin erklärt westlichen Traumtänzern die Lage</t>
         </is>
       </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -26364,6 +29004,11 @@
           <t>Ex-US-Präsident Obama wird „Prepper“ hortet zu Hause Propangas in Riesentanks</t>
         </is>
       </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -26413,6 +29058,11 @@
           <t>Umfrage deckt auf: 83 Prozent der Deutschen wünschen sich besseren Grenzschutz</t>
         </is>
       </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -26462,6 +29112,11 @@
           <t>Der Ukrainer nutzt den Krieg und die Faschisten, um sich an der Macht zu halten. Preisfrage: Wann lief die letzte 20-Uhr-Tagesschau ohne Beitrag über Ukraines Präsidenten Selenskyj – albern kostümiert in NATO-Oliv, Waffen und Geld fordernd? „Selenskyj“ im Suchfeld auf tagesschau.de ergibt für die letzten drei Monate mehr als 1 400 Treffer. Tagesschau.de listet darunter mehr als 500-mal Selenskyj-Videos: Heldenverehrung für einen ferngesteuerten Gewaltherrscher, der den Kriegszustand zur Festigung der eigenen Position verlängert und dafür täglich hunderte Menschenleben opfert. Hingegen verschwieg die Tagesschau den weltweit beachteten Rat des einstigen US-Außenministers Henry Kissinger, Selenskyj solle zur Vermeidung einer gesamteuropäischen Katastrophe freiwillig Territorium an Russland abtreten und Frieden schließen. Kissingers Realismus passte der giftgrün-linientreuen ARD-aktuell-Redaktion ersichtlich nicht in den Propagandakram.</t>
         </is>
       </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -26511,6 +29166,11 @@
           <t>Ausweitung der legalen Migration durch EU ist abzulehnen!</t>
         </is>
       </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -26560,6 +29220,11 @@
           <t>Hohe Kosten und kalte Füße</t>
         </is>
       </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -26609,6 +29274,11 @@
           <t>Sanktionen: Russland gewinnt den Wirtschaftskrieg</t>
         </is>
       </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -26658,6 +29328,11 @@
           <t>Mit Marine Le Pen übernimmt eine Rechtspopulistin die Fraktionsführung</t>
         </is>
       </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -26707,6 +29382,11 @@
           <t>Botschafter grillt Politiker</t>
         </is>
       </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -26756,6 +29436,11 @@
           <t>Jetzt bestätigt auch Pfizer-Chef : Impfungen gegen Corona-Infektionen praktisch wirkungslos</t>
         </is>
       </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -26805,6 +29490,11 @@
           <t>Der Krieg fiel nicht vom Himmel! (I) – „By the grace of God America won the Cold War!“</t>
         </is>
       </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -26854,6 +29544,11 @@
           <t>Westliche Sanktionen bewirken das Gegenteil: Rußlands Energie-Einnahmen höher als vor dem Krieg</t>
         </is>
       </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -26903,6 +29598,11 @@
           <t>Putin: Trotz der Versuche, die Ära der unipolaren Welt zu erhalten, ist sie nun zu Ende – die herrschende Elite des Westens lebt in einer Traumwelt</t>
         </is>
       </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -26952,6 +29652,11 @@
           <t>Die wichtigsten Fragen und Antworten zum NATO-Beitritt von Finnland und Schweden</t>
         </is>
       </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -27001,6 +29706,11 @@
           <t>Die unendliche Farce der US-Sanktionen gegen Russland</t>
         </is>
       </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -27050,6 +29760,11 @@
           <t>Der Zank um die Grundrechte</t>
         </is>
       </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -27099,6 +29814,11 @@
           <t>Sich gegen das Wuhan-Coronavirus (Covid-19) „impfen“ zu lassen, stoppt die Ausbreitung, oder? Falsch. Die neuesten Daten zeigen, dass je geimpfter ein Zustand geimpft wird, desto höher ist die Rate von Omikron (mönlich) und anderen „Varianten“.</t>
         </is>
       </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -27148,6 +29868,11 @@
           <t>Befürchtet Bürgerkrieg als Folge der Masseneinwanderung.</t>
         </is>
       </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -27197,6 +29922,11 @@
           <t>Der neue globale Kalte Krieg der NATO ist jetzt offiziell</t>
         </is>
       </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -27246,6 +29976,11 @@
           <t>G20-Gipfel: Lawrow wirft Westen vor, russische Panzer mit Supermagnet auf ukrainisches Territorium gezogen zu haben</t>
         </is>
       </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -27295,6 +30030,11 @@
           <t>"Wir finden kaum noch Leute" – Chef von MiesBezahlteDrecksjobs GmbH beklagt Personalmangel</t>
         </is>
       </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -27344,6 +30084,11 @@
           <t>Die Ukraine durch Diebstahl russischen Vermögens "aus der Asche erheben" – von der Leyen in Davos</t>
         </is>
       </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -27393,6 +30138,11 @@
           <t>Die weltweit größten Sponsoren eigener imperialer Macht fordern die "Dekolonisierung" Russlands</t>
         </is>
       </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -27442,6 +30192,11 @@
           <t>Europaabgeordneter über Trudeau: „Er benimmt sich wie ein Tyrann, wie ein Diktator“!</t>
         </is>
       </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>ge</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -27491,6 +30246,11 @@
           <t>Der „Preis“, den Russland für den Einsatz militärischer Gewalt zahlen muss</t>
         </is>
       </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -27540,6 +30300,11 @@
           <t>Die Ukrainische Armee und die „Atlantistische Internationale“</t>
         </is>
       </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -27589,6 +30354,11 @@
           <t>Covid, Vaia: „Neue Omicron-Variante durchsticht Impfstoffe, nutzloser Lockdown“ •</t>
         </is>
       </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -27638,6 +30408,11 @@
           <t>Letta, Freiheit und der Impfstoff</t>
         </is>
       </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -27687,6 +30462,11 @@
           <t>Covid, wissenschaftlicher Artikel untersucht die Beweise zu den Folgen von Impfstoffen: „Sie sind weder sicher noch wirksam“</t>
         </is>
       </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -27736,6 +30516,11 @@
           <t>Kreml: Iran und Russland sind bereit, im bilateralen Handel auf den US-Dollar zu verzichten</t>
         </is>
       </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -27785,6 +30570,11 @@
           <t>Ecr, Fitto: EU-NATO kooperieren immer mehr, um die Auswahl der Länder zu gewährleisten, die dem Bündnis beitreten möchten</t>
         </is>
       </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -27834,6 +30624,11 @@
           <t>EMA und ECDC sagen Ja zur 4. Dosis. Mittlerweile allein im letzten Jahr 2 Millionen Meldungen über Impfschäden</t>
         </is>
       </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -27883,6 +30678,11 @@
           <t>Die 16 größten Lügen, die die US-Regierung der Welt über den Krieg in der Ukraine erzählt</t>
         </is>
       </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -27932,6 +30732,11 @@
           <t>Draghi vs. Putin, Meluzzi: „Ich erkläre die Beziehung zwischen Italien und Biden“</t>
         </is>
       </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -27981,6 +30786,11 @@
           <t>Ärzte werfen vor: „Migranten kommen nach Italien, um sich kostenlos behandeln zu lassen“</t>
         </is>
       </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -28030,6 +30840,11 @@
           <t>China und Russland, das Geheimnis um die Beziehungen zwischen Putin und Xi Jinping bricht aus. Und der Chat mit Spitznamen erscheint</t>
         </is>
       </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -28079,6 +30894,11 @@
           <t>Affenpocken, WHO warnt Europa: „Fälle haben sich verdreifacht“. Das Virus breitet sich aus</t>
         </is>
       </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -28128,6 +30948,11 @@
           <t>Die Ukraine kann den Krieg gewinnen, helfen wir ihr jetzt</t>
         </is>
       </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -28177,6 +31002,11 @@
           <t>Flüchtlingstragödie in Lampedusa, 7 erlagen der Unterkühlung, „Inakzeptable Tragödie, gleichgültige EU“</t>
         </is>
       </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -28226,6 +31056,11 @@
           <t>„Nicht sehr christlich und sehr faschistisch“, das Porträt von Pillon laut Paola Turci</t>
         </is>
       </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -28275,6 +31110,11 @@
           <t>Die Homophobie des Patriarchen von Moskau hat den kriminellen Charakter der russischen Invasion offenbart</t>
         </is>
       </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -28324,6 +31164,11 @@
           <t>Ist Italien zurück? Der Konflikt mit der Türkei und einige Hypothesen zur Außenpolitik von Mario Draghi</t>
         </is>
       </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -28373,6 +31218,11 @@
           <t>Die USA und die EU beginnen zu erkennen, dass die Ukraine sie teuer zu stehen kommt</t>
         </is>
       </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -28422,6 +31272,11 @@
           <t>Wenn Erdogan es sich erlaubt, Draghi Unterricht in Demokratie zu erteilen</t>
         </is>
       </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -28471,6 +31326,11 @@
           <t>Deutschland, die grüne Dame auf dem Rost, der Traum vom Kanzleramt schwindet</t>
         </is>
       </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -28520,6 +31380,11 @@
           <t>Ukraine, Meloni: „Die Linke hat jetzt den Unterschied zwischen echten Flüchtlingen und Wirtschaftsflüchtlingen verstanden“</t>
         </is>
       </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -28569,6 +31434,11 @@
           <t>ZUR ABSTIMME! ZUR ABSTIMME! DIE SPRECHENDEN POLITIKER</t>
         </is>
       </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -28618,6 +31488,11 @@
           <t>Abbau von Positionen in der Ukraine und Sicherheit in Europa</t>
         </is>
       </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -28667,6 +31542,11 @@
           <t>Mit Israel hat die russische Geduld ihre Grenzen erreicht</t>
         </is>
       </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -28716,6 +31596,11 @@
           <t>Draghi beim G7-Gipfel „Putin darf nicht gewinnen, vereint in der Unterstützung der Ukraine“ »</t>
         </is>
       </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -28765,6 +31650,11 @@
           <t>Mehr Geld für Einwanderer als für Rentner: 72 % haben eine niedrigere Rente als die Flüchtlingsrente</t>
         </is>
       </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -28814,6 +31704,11 @@
           <t>Landungen + 30 %: Islamische Bombe an italienischen Stränden</t>
         </is>
       </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -28863,6 +31758,11 @@
           <t>1 – Trumps Kundgebung für die Wahlen in Alaska: „Mit Treibhauseffekt mehr Häuser mit Meerblick“</t>
         </is>
       </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -28912,6 +31812,11 @@
           <t>Unsere Jugend ist alarmiert: Nachdem sie mit Covid verblüfft wurde, versetzt ihnen die Kriegspropaganda der Regimemedien den letzten Schlag: Sie ruinieren ganze Generationen</t>
         </is>
       </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -28961,6 +31866,11 @@
           <t>Regierung. Chaos, weil Mattarella, Draghi, Conte, Salvini, Letta gewinnen müssen</t>
         </is>
       </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -29010,6 +31920,11 @@
           <t>Es ist das übliche Berlusconi: „Forza Italia bei 20 %, wir werden den Premierminister wählen.“ Über Überläufer: „Sie werden verschwinden wie Alfano“</t>
         </is>
       </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -29059,6 +31974,11 @@
           <t>DRAGHI FÄLLT, PUTIN GENIEßT - GRAMELLINI: „ENTSCHULDIGUNG FÜR DAS BÖSSE DENKEN (ES WIRD DIE HITZE SEIN), ABER IN ANBETRACHT DER GEMEINSAMEN POSITION VON CONTE UND SALVINI ZUM KRIEG IST DAS WAHRE GEHEIMNIS NICHT, DASS DIE REGIERUNG GEFALLEN IST, SONDERN, WIE SIE ES GESCHAFFT HAT, BIS GESTERN DAUERZUHALTEN…“</t>
         </is>
       </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -29108,6 +32028,11 @@
           <t>The New York Times: Draghis Rücktritt ist eine potenzielle Katastrophe für Europa</t>
         </is>
       </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -29157,6 +32082,11 @@
           <t>Draghi steht kurz vor seinem Rücktritt, genau zu dem Zeitpunkt, als Europa ihn braucht</t>
         </is>
       </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -29206,6 +32136,11 @@
           <t>„Draghi bleibt“, die Farce des Appells der Bürgermeister. Um 9.30 Uhr Debatte im Senat</t>
         </is>
       </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -29255,6 +32190,11 @@
           <t>Di Maio: Conte wird nicht für Draghi stimmen, er hat auf die Wahlen gewettet, aber ein Zusammenbruch erwartet ihn</t>
         </is>
       </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -29304,6 +32244,11 @@
           <t>Hotspot Lampedusa kollabiert, Pisano: „Von der Regierung geschickte nutzlose Taxischiffe, wir sind die Einzigen, die die italienischen Grenzen verteidigen“</t>
         </is>
       </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -29353,6 +32298,11 @@
           <t>dessen kleine Hand es ist, die aus der Staatsanwaltschaft von Perugia Dokumente herausgelassen hat, die der Geheimhaltung unterliegen und</t>
         </is>
       </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -29402,6 +32352,11 @@
           <t>Die Inflation macht dem Staat nur Freude! - Dank des Preiswachstums stößt die Staatskasse an</t>
         </is>
       </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -29451,6 +32406,11 @@
           <t>Brüssel muss sich mit der Realität auseinandersetzen: Es ist Zeit, sich mit Putin auseinanderzusetzen, sonst kommt es zu einer Rezession</t>
         </is>
       </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -29500,6 +32460,11 @@
           <t>Migranten werden von Russland als Waffen eingesetzt? „Von der Wagner-Gruppe nach Italien gedrängt“</t>
         </is>
       </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -29549,6 +32514,11 @@
           <t>Terni, radikale Linke auf der Straße gegen Putin, gegen die NATO und gegen die Draghi-Regierung. Nein zum Waffenversand in die Ukraine</t>
         </is>
       </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -29598,6 +32568,11 @@
           <t>Kinder sind sicher, wenn Eltern geimpft sind: neue Daten zu Covid</t>
         </is>
       </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -29647,6 +32622,11 @@
           <t>Der Klimawandel zerstört die menschliche Gesundheit. Der Terror von Walter Ricciardi</t>
         </is>
       </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -29696,6 +32676,11 @@
           <t>Verpflichtungen und Versäumnisse: Omicron wird bestehen, Rechte und Freiheiten jedoch nicht</t>
         </is>
       </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -29745,6 +32730,11 @@
           <t>Wer bedroht den Frieden in der Ukraine?</t>
         </is>
       </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -29794,6 +32784,11 @@
           <t>Ukrainische Militäringenieure bauen die Möbius-Straßenstreifen wieder auf und stoppen den russischen Vormarsch</t>
         </is>
       </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -29843,6 +32838,11 @@
           <t>G7 in München: Sie sind so unbedeutend, dass selbst die Demonstranten sich nicht mehr darum kümmern</t>
         </is>
       </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -29892,6 +32892,11 @@
           <t>DER VIZEPRÄSIDENT DES RUSSISCHEN SICHERHEITSRATS greift den Westen erneut an: „Das Niveau der Politiker ist gesunken. Es ist jedem klar, dass Mario Draghi nicht Silvio Berlusconi und Olaf Schulz nicht Angela Merkel ist“ – „Die großen Führer der Vergangenheit waren keine Russenfeinde, und sie sind es.“ WURDEN DURCH EINE NEUE GENERATION SCHWACHER MENSCHEN ERSETZT, DIE SICH TECHNOKRATEN BENENNEN ...“</t>
         </is>
       </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -29941,6 +32946,11 @@
           <t>Für den ehemaligen Vizepräsidenten des National Intelligence Council „hat die Ukraine den Krieg verloren“</t>
         </is>
       </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -29990,6 +33000,11 @@
           <t>„HINTER PUTINS IMPERIALEN TRAUM STECKT EINE WIRTSCHAFTLICHE BERECHNUNG“</t>
         </is>
       </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -30039,6 +33054,11 @@
           <t>Wir unterstützen 10.000 Kinder von Einwanderern: Es ist unmöglich, sie auszuweisen, selbst wenn sie vergewaltigen</t>
         </is>
       </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -30088,6 +33108,11 @@
           <t>Meloni schlechter als Bolsonaro und Trump: „Ideologischer Umweltschutz, Überprüfung der Klimastrategien der EU“</t>
         </is>
       </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -30137,6 +33162,11 @@
           <t>Fast 11.000 Migranten sind dieses Jahr bereits gelandet. Meloni: «Seeblockade ist die einzige Lösung»</t>
         </is>
       </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -30186,6 +33216,11 @@
           <t>NATO-Kommissar Kiew: „Wir werden die russische Krim niemals akzeptieren“</t>
         </is>
       </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -30235,6 +33270,11 @@
           <t>Der Draghistan-Krieg</t>
         </is>
       </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -30284,6 +33324,11 @@
           <t>Moskaus Raketen auf Odessa: Michel muss Zuflucht suchen. Selenskyj: „Putin wie Hitler“</t>
         </is>
       </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -30333,6 +33378,11 @@
           <t>Nachhaltiges Finanzwesen und EU-Taxonomie: Was ändert sich?</t>
         </is>
       </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -30382,6 +33432,11 @@
           <t>China setzt Raketen und Kampfflugzeuge ein, um Taiwan zu bedrohen</t>
         </is>
       </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -30431,6 +33486,11 @@
           <t>Ukraine-EffektJetzt ist auch Island versucht, der EU beizutreten</t>
         </is>
       </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -30480,6 +33540,11 @@
           <t>Hochspannung in Taiwan: „Chinesische Militärschiffe und Flugzeuge überqueren die Mittellinie der Meerenge“</t>
         </is>
       </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -30529,6 +33594,11 @@
           <t>NGOs dürfen sie nicht bestrafen: Das EU-Urteil verurteilt Italien zur Invasion</t>
         </is>
       </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -30578,6 +33648,11 @@
           <t>Salvini-Berlusconi gegen „den Amerikaner“ Mario Draghi: Hintergründe, wie der Krieg den Premierminister in die Luft jagen kann</t>
         </is>
       </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -30627,6 +33702,11 @@
           <t>Die Zukunft des HandelsDeglobalisierung oder neue Globalisierung?</t>
         </is>
       </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -30676,6 +33756,11 @@
           <t>Für italienische Familien ist die Preiserhöhung ein 9-Milliarden-Schlag</t>
         </is>
       </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -30725,6 +33810,11 @@
           <t>Biden und Xi Jinping einigen sich auf ein persönliches Treffen, doch die Spannungen in Bezug auf Taiwan bleiben hoch</t>
         </is>
       </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -30774,6 +33864,11 @@
           <t>Orlando, oder aktueller Ministerpräsident, beschützt von Napolitano und Rivale von Calenda</t>
         </is>
       </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -30823,6 +33918,11 @@
           <t>Selenskyj möchte, dass die USA Russland als „Terrorstaat“ bezeichnen. Es lebe die Diplomatie</t>
         </is>
       </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -30872,6 +33972,11 @@
           <t>Erich Vad, Merkels ehemaliger Berater: „USA und London können uns in den Dritten Weltkrieg hineinziehen“</t>
         </is>
       </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -30921,6 +34026,11 @@
           <t>Cannabis, Heimanbau entkriminalisiert. Ja, aus der Kammer. Delmastro (FdI): Nein zur Drogenkultur</t>
         </is>
       </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -30970,6 +34080,11 @@
           <t>US-Plan scheitert in der Ukraine</t>
         </is>
       </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -31019,6 +34134,11 @@
           <t>Russland-Ukraine, Zusammenstöße in der Nähe des Kernkraftwerks Tschernobyl: Welche Risiken bestehen?</t>
         </is>
       </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -31068,6 +34188,11 @@
           <t>Der kriminelle Plan der Linken zur Ausrottung der Italiener: Abtreibung, Familienzusammenführung und offene Häfen</t>
         </is>
       </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -31117,6 +34242,11 @@
           <t>HANDELSBLATT: Der Westen beobachtet verzweifelt, wie Putin eine neue Weltordnung schafft</t>
         </is>
       </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -31166,6 +34296,11 @@
           <t>Estland: Die Regierung beschließt, alle sowjetischen Denkmäler aus dem öffentlichen Raum zu entfernen</t>
         </is>
       </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -31215,6 +34350,11 @@
           <t>Russland, „Bloomberg“: Die G7 kämpft darum, internationale Verbündete für eine Ausweitung der Sanktionen zu finden</t>
         </is>
       </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -31264,6 +34404,11 @@
           <t>Die Bischöfe fordern in Italien das Recht der Schule, doch im Vatikan gibt es nur das Recht des Blutes</t>
         </is>
       </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -31313,6 +34458,11 @@
           <t>Ukraine, Selenskyj: „Lass Gerechtigkeit geschehen, lass die Welt untergehen“</t>
         </is>
       </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -31362,6 +34512,11 @@
           <t>Warum essen Menschen Fleisch, auch wenn es sich negativ auf den Planeten und ihre Gesundheit auswirkt?</t>
         </is>
       </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -31411,6 +34566,11 @@
           <t>NATO-Marionette Stoltenberg drängt auf Krieg gegen Russland</t>
         </is>
       </c>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -31460,6 +34620,11 @@
           <t>Affenpocken in Italien, Bootsnotfall und Schwule. WER: „Berühren Sie niemanden, der Fieber hat“</t>
         </is>
       </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -31509,6 +34674,11 @@
           <t>Putins Rede auf dem BRICS-Gipfel (und unten, was Draghi über Sanktionen sagte)</t>
         </is>
       </c>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -31558,6 +34728,11 @@
           <t>Brasilien: Nein zu Sanktionen gegen Russland, sonst gibt es Welthunger. Die Realwirtschaft übertrifft die Papierwirtschaft</t>
         </is>
       </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -31607,6 +34782,11 @@
           <t>Die Tentakel der NATO von Europa bis Lateinamerika</t>
         </is>
       </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -31656,6 +34836,11 @@
           <t>China Daily: „Wirtschaftliche Probleme kommen auf Europa zu“</t>
         </is>
       </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -31705,6 +34890,11 @@
           <t>Coronavirus, Bolsonaro: „In Italien sterben viele Menschen, weil es ein Land der alten Menschen ist“</t>
         </is>
       </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -31754,6 +34944,11 @@
           <t>Russland-Ukraine-Krieg: Bolsonaros Brasilien bleibt neutral. Aber der Präsident ist pro-russisch</t>
         </is>
       </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -31803,6 +34998,11 @@
           <t>Washington weigert sich, auf Russland und China zu hören</t>
         </is>
       </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -31852,6 +35052,11 @@
           <t>Salvini-Orban, Einigkeit in Bezug auf Migranten und die europäische Mitte-Rechts-Partei</t>
         </is>
       </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -31901,6 +35106,11 @@
           <t>Giorgia Meloni und Marine Le Pen, weil der Krieg in der Ukraine die nationalistischen Parteien stärker gemacht hat</t>
         </is>
       </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -31950,6 +35160,11 @@
           <t>Kommunistische Regime und Gesundheitsdiktaturen: dieselbe Geschichte, dasselbe Ende</t>
         </is>
       </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -31999,6 +35214,11 @@
           <t>UKRAINE. GEOPOLITISCHES DESIGN DER USA. Europas selbstmörderische Russlandphobie</t>
         </is>
       </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -32048,6 +35268,11 @@
           <t>Warum fordert Europa nicht ein Ende dieses Krieges?</t>
         </is>
       </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -32097,6 +35322,11 @@
           <t>Chinas neueste Warnung an Amerika</t>
         </is>
       </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -32146,6 +35376,11 @@
           <t>Putin, die unabhängige Umfrage, entlarvt eine weitere Lüge: Er erfreut sich bei seinen Anhängern immer größerer Beliebtheit und die Sanktionen haben großen Eindruck auf die sehr reichen Oligarchen gemacht</t>
         </is>
       </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -32195,6 +35430,11 @@
           <t>Durch die Aufstände in Zentralasien strecken die Vereinigten Staaten ihre Tentakel Richtung Russland und China aus</t>
         </is>
       </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -32244,6 +35484,11 @@
           <t>China: Covid-Tracing-App zur Verhinderung von Protesten eingesetzt</t>
         </is>
       </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -32293,6 +35538,11 @@
           <t>Regierung der Republik zwischen Legitimität und (verlorener) Legitimität</t>
         </is>
       </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -32342,6 +35592,11 @@
           <t>Saudi-Arabien hat seine Importe von russischem Öl im zweiten Quartal 2022 verdoppelt</t>
         </is>
       </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -32391,6 +35646,11 @@
           <t>Impfstoff, jetzt werden die No-Vax-Menschen auch zu denen mit zwei Dosen. Verstehen Sie jetzt, warum man Ihnen sagt, dass die Intensivstation voller No Vax ist?</t>
         </is>
       </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -32440,6 +35700,11 @@
           <t>Covid und Impfstoff, Galli: Die Pflicht bleibt für über 50-Jährige bestehen. Keine Amnestie für Impfgegner</t>
         </is>
       </c>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -32489,6 +35754,11 @@
           <t>Lieber Draghi, es sind die Geimpften, die die Intensivstationen verstopfen</t>
         </is>
       </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -32538,6 +35808,11 @@
           <t>Covid führt dazu, dass Anti-Vaxing zurückgeht. Das Vertrauen in Impfstoffe wächst, 9 von 10 geben an, dass sie wirksam sind</t>
         </is>
       </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -32587,6 +35862,11 @@
           <t>Die Wahlen in Frankreich und der sensationelle Flop der EU-Regierungsparteien</t>
         </is>
       </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -32636,6 +35916,11 @@
           <t>EU-Rechnungshof lehnt REPowerEu-Plan der Kommission ab – Europa</t>
         </is>
       </c>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -32685,6 +35970,11 @@
           <t>EU: „Kritik am Gasplan ist natürlich, aber es bedarf einer gemeinsamen Antwort“</t>
         </is>
       </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -32734,6 +36024,11 @@
           <t>Selenskyj: „Putin will wie Hitler die Endlösung. Ohne ein Abkommen wird es einen dritten Weltkrieg geben“</t>
         </is>
       </c>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -32783,6 +36078,11 @@
           <t>„Putin hat keine Raketen mehr. Jetzt kann Kiew gewinnen“</t>
         </is>
       </c>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -32832,6 +36132,11 @@
           <t>Pride, Zan: „Rechte nutzt Menschenrechte für Wahlkonsens, aber wir werden gewinnen“</t>
         </is>
       </c>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -32881,6 +36186,11 @@
           <t>„Wir stehen nicht unter dem Dach der NATO. Wir sind das Dach der NATO“</t>
         </is>
       </c>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -32930,6 +36240,11 @@
           <t>George Soros entpuppt sich als wichtiger Geldgeber der „Global Climate Strike“-Gruppen</t>
         </is>
       </c>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -32979,6 +36294,11 @@
           <t>Zensur und Rechtfertigungismus: Die Linke vertuscht die Gewalt von Einwanderern in Peschiera</t>
         </is>
       </c>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -33028,6 +36348,11 @@
           <t>Die Vereinigten Staaten beabsichtigen, gegen Russland Krieg zu führen, und zwar bis zum Ende ihrer Macht</t>
         </is>
       </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -33077,6 +36402,11 @@
           <t>Ukrainischer Krieg: Es herrscht ein Hauch von Freiheit, treffen Sie die richtige Wahl und entscheiden Sie sich immer für den Frieden</t>
         </is>
       </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -33126,6 +36456,11 @@
           <t>Iranische Atomgespräche scheitern: Droht ein weiterer Krieg?</t>
         </is>
       </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -33175,6 +36510,11 @@
           <t>Moskau und Peking: Die USA wollen Insekten in biologische Waffen verwandeln</t>
         </is>
       </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -33224,6 +36564,11 @@
           <t>Strategika – Der Anfang vom Ende für die ukrainische Armee?</t>
         </is>
       </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -33273,6 +36618,11 @@
           <t>Covid, während Europa sich dem „Japaner“ zuwendet, bleibt die Hoffnung im Pandemie-Dschungel</t>
         </is>
       </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
@@ -33322,6 +36672,11 @@
           <t>DIE FOLGE PUTINS BRINGT ORBAN IN DEN ABGRUND - IN BUDAPEST SIND SEIT FÜNF TAGEN WÜTENDE PROTESTDEMONSTRATIONEN GEGEN DIE VON ORBAN VERORDNETE STEUERREFORM - SEIT SEINER VIERTEN WIEDERWAHL MUSS SICH DER UNGARISCHE PREMIERESPRÄSIDENT ZUM ERSTEN MAL MASSENKETTEN STELLEN - WAS IHN KOSTENLOS IST, IST DIE PRO-PUTIN-LINIE ZU GAS UND ÖL: DIE ENERGIEKRISE HAT IHN JETZT ZWISCHEN, SUBVENTIONEN FÜR GESCHÜTZTE KATEGORIEN ABZUFÜHREN. MITTLEREN IST DIE INFLATION SEHR HOCH…</t>
         </is>
       </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -33371,6 +36726,11 @@
           <t>China bereitet sich auf den Krieg vor</t>
         </is>
       </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -33420,6 +36780,11 @@
           <t>Nicaraguas Präsident Daniel Ortega: „Russland kämpft gegen die Nazis in der Ukraine“</t>
         </is>
       </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -33469,6 +36834,11 @@
           <t>Hier ist der „süße“ Plan der Regierung: Kürzungen bei Strom und Gas. Und eine schöne Ausgangssperre. Sagen Sie uns jetzt, dass Sanktionen funktionieren</t>
         </is>
       </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -33518,6 +36888,11 @@
           <t>„Geh nicht allein“: das surreale französische Handbuch gegen Angriffe von Einwanderern</t>
         </is>
       </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -33567,6 +36942,11 @@
           <t>Die Lügen der NATO implodieren... Sie sagten dem Regime in Kiew: „Zahlen Sie den Preis für den Frieden“</t>
         </is>
       </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -33616,6 +36996,11 @@
           <t>Österreich, Kurz: „Wir heißen afghanische Flüchtlinge nicht willkommen, wir haben zu viele. Keine illegale Einwanderung mehr“</t>
         </is>
       </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -33665,6 +37050,11 @@
           <t>Draghi trifft (nur) seine Freundin Letta. Vom Schlamassel zur Mitte-Links-Regierung?</t>
         </is>
       </c>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -33714,6 +37104,11 @@
           <t>Nicht schon wieder! Biden enthüllt weitere 700 Millionen Dollar für die Waffen der Ukraine!</t>
         </is>
       </c>
+      <c r="P679" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -33763,6 +37158,11 @@
           <t>Mitteilungen von Präsident Draghi an den Senat der Republik</t>
         </is>
       </c>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -33812,6 +37212,11 @@
           <t>Meloni, Giuliani (ehemaliger Bürgermeister von New York): Es wird die Italienerin Margaret Thatcher sein.</t>
         </is>
       </c>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -33861,6 +37266,11 @@
           <t>Landungen und Infektionen: Die Plage illegaler Einwanderer dringt in den neuen Covid-Notstand ein</t>
         </is>
       </c>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -33910,6 +37320,11 @@
           <t>Selenskyj: Bereiten wir eine Armee von einer Million Soldaten vor •</t>
         </is>
       </c>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -33959,6 +37374,11 @@
           <t>KLIMA: Die globale Erwärmung wird noch LANGE anhalten und das erste Opfer könnte der Mensch sein. Eine Studie verrät es</t>
         </is>
       </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -34008,6 +37428,11 @@
           <t>Die UN fordern Kiew, Moskau, die USA und die EU auf, die Abkommen über russischen und ukrainischen Weizen einzuhalten</t>
         </is>
       </c>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -34057,6 +37482,11 @@
           <t>99 % wollten den Green Pass nicht verlängern und haben ihn sogar verlängert. Demokratie in Europa</t>
         </is>
       </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
@@ -34106,6 +37536,11 @@
           <t>Niederlande: 30.000 Landwirte ziehen mit Traktoren umher, um gegen die Umweltpolitik der Regierung zu protestieren</t>
         </is>
       </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
@@ -34155,6 +37590,11 @@
           <t>Bonino: „Italien muss jährlich 400.000 Einwanderer importieren, um die Italiener zu ersetzen“</t>
         </is>
       </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
@@ -34204,6 +37644,11 @@
           <t>ÜBER 1 MILLION ILLEGALE EINWANDERER IN DEN USA, SEIT BIDEN AN DIE MACHT KOMMT</t>
         </is>
       </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
@@ -34253,6 +37698,11 @@
           <t>Washington ist bereit, Sanktionskriege bis zum letzten Europäer zu führen</t>
         </is>
       </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
@@ -34302,6 +37752,11 @@
           <t>Sie vergewaltigen Frauen, alte Menschen und Kinder: Einwanderer, die außer Kontrolle geraten</t>
         </is>
       </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -34351,6 +37806,11 @@
           <t>Die NATO verspricht, Melilla vor Angriffen zu schützen, Lampedusa jedoch nicht</t>
         </is>
       </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
@@ -34400,6 +37860,11 @@
           <t>St. Petersburg bereitet die Bühne für den Krieg der Wirtschaftskorridore</t>
         </is>
       </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -34449,6 +37914,11 @@
           <t>Zelensky-Hologramme: Der Krieg projiziert uns in die Zukunft</t>
         </is>
       </c>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
@@ -34498,6 +37968,11 @@
           <t>Sanktionen gegen Oligarchen, Patriarch Kirill fordert die Gläubigen auf, für sein Portemonnaie zu beten</t>
         </is>
       </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
@@ -34547,6 +38022,11 @@
           <t>Lukaschenko an die „internationalen Betrüger“ der Pandemie: „Genug!“</t>
         </is>
       </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
@@ -34596,6 +38076,11 @@
           <t>Es war nicht Covid, das Menschen sterben ließ, sondern die Lockdowns.</t>
         </is>
       </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
@@ -34645,6 +38130,11 @@
           <t>Draghis begründetes Risiko: über 50.000 Tote seit seinem Amtsantritt als Premierminister</t>
         </is>
       </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -34694,6 +38184,11 @@
           <t>Calenda will Ungarn aus der EU verlassen. Aber dort regieren die Gewinner, nicht die Verlierer (wie hier die Demokratische Partei)</t>
         </is>
       </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
@@ -34743,6 +38238,11 @@
           <t>Türkischer Verteidigungsminister: Russland hatte nichts mit der Bombardierung von Odessa zu tun</t>
         </is>
       </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
@@ -34792,6 +38292,11 @@
           <t>Entvölkerung durch Impfungen</t>
         </is>
       </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
@@ -34841,6 +38346,11 @@
           <t>Das Anti-Putin-Dilemma der deutschen Grünen: „Wie viele Minuten kann der Schauer dauern?“</t>
         </is>
       </c>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
@@ -34890,6 +38400,11 @@
           <t>Orban: „EU ändert Strategie, Westen verhandelt zwischen Moskau und Kiew“</t>
         </is>
       </c>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
@@ -34939,6 +38454,11 @@
           <t>Die ukrainischen Häfen sind wieder in Betrieb. Moskau: „Russische Exporte starten wieder“</t>
         </is>
       </c>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
@@ -34988,6 +38508,11 @@
           <t>Abrignani (Cts) zu Covid: „Impfpflicht, solange das Virus zirkuliert, vielleicht Jahre“</t>
         </is>
       </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
@@ -35037,6 +38562,11 @@
           <t>Johnsons Händedruck mit bin Salman... die „moralische“ Lektion!</t>
         </is>
       </c>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
@@ -35086,6 +38616,11 @@
           <t>Die Türkei will keine „Unterstützer des Terrorismus“ in der NATO</t>
         </is>
       </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
@@ -35135,6 +38670,11 @@
           <t>„Abtreibung sollte legal, sicher und kostenlos sein.“ Baldige Abstimmung im Sejm: Wer wird dafür sein?</t>
         </is>
       </c>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
@@ -35184,6 +38724,11 @@
           <t>Ein Referendum zur Abtreibung? Scheuring-Wielgus: Bei Volksabstimmungen reden wir nicht über Menschenrechte</t>
         </is>
       </c>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
@@ -35233,6 +38778,11 @@
           <t>Legale Abtreibung. „Bei dieser Abstimmung war die Wahl sehr einfach, Sie sind entweder für Frauen oder dagegen.“</t>
         </is>
       </c>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
@@ -35282,6 +38832,11 @@
           <t>Kim Jong Un will Putins Armee unterstützen. Über diese Ausrüstung verfügt Nordkorea.</t>
         </is>
       </c>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
@@ -35331,6 +38886,11 @@
           <t>Die Razem-Partei befragt die Regierung zum Thema Atomkraft. „Es fehlt der wirkliche Wille zur Umsetzung“</t>
         </is>
       </c>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
@@ -35380,6 +38940,11 @@
           <t>VERSCHIEDENE FRONTEN EINES KRIEGES</t>
         </is>
       </c>
+      <c r="P713" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
@@ -35429,6 +38994,11 @@
           <t>Eine kontroverse Meinung eines deutschen Politikers. „Nicht nur Russland, auch die USA sind böse“</t>
         </is>
       </c>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
@@ -35478,6 +39048,11 @@
           <t>Neue Generäle der polnischen Armee. Der Präsident stimmte den Nominierungen zu</t>
         </is>
       </c>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
@@ -35527,6 +39102,11 @@
           <t>Putin gab seine Stimme. Zittern die Franzosen schon wieder mit den Hosen?</t>
         </is>
       </c>
+      <c r="P716" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
@@ -35576,6 +39156,11 @@
           <t>Stanisław Michalkiewicz: 600 Milliarden Dollar für den Export des Kommunismus</t>
         </is>
       </c>
+      <c r="P717" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
@@ -35625,6 +39210,11 @@
           <t>„Auf Polens Seite“. Der Bund startete eine Programmoffensive</t>
         </is>
       </c>
+      <c r="P718" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
@@ -35674,6 +39264,11 @@
           <t>Über hundert Coronavirus-Infektionen im Zusammenhang mit einem Riegel. „Gefährliche Welle“ in Peking</t>
         </is>
       </c>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
@@ -35723,6 +39318,11 @@
           <t>„Chinesisches Virus“ – von der Verschwörungstheorie zur ernsten Hypothese</t>
         </is>
       </c>
+      <c r="P720" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
@@ -35772,6 +39372,11 @@
           <t>Neues Coronavirus in Schweden entdeckt. Haben wir etwas zu befürchten?</t>
         </is>
       </c>
+      <c r="P721" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
@@ -35821,6 +39426,11 @@
           <t>Der ukrainische Nationalismus breitet sich in Polen mit alarmierender Geschwindigkeit aus. Bald werden wir für Wolhynien um Vergebung bitten.</t>
         </is>
       </c>
+      <c r="P722" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
@@ -35870,6 +39480,11 @@
           <t>Dr. Bogusław Rogalski: Der Besuch von Macron, Scholz und Draghi in Kiew ist ein zynischer Säufer der Staatsoberhäupter, die Putin im Laufe der Jahre mit ihrer Politik der Zusammenarbeit mit Russland hervorgebracht und mutig gemacht haben</t>
         </is>
       </c>
+      <c r="P723" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
@@ -35919,6 +39534,11 @@
           <t>Macron, Scholz, Draghi und Iohannis bei einem Besuch (Auslandsreise) in der Ukraine. Es gibt nichts Schöneres als einen weiteren Tag im Theater.</t>
         </is>
       </c>
+      <c r="P724" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
@@ -35968,6 +39588,11 @@
           <t>Frontex: Es gab viel weniger Flüchtlinge als vom Grenzschutz gemeldet</t>
         </is>
       </c>
+      <c r="P725" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
@@ -36017,6 +39642,11 @@
           <t>Kukiz über die Ungeimpften: Wenn jemand sich erhängen will, kann er das tun</t>
         </is>
       </c>
+      <c r="P726" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="n">
@@ -36066,6 +39696,11 @@
           <t>Das Banner „Impfung macht frei“ ist kein Arbeitsunfall. So spielt der Bund mit der Epidemie</t>
         </is>
       </c>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="n">
@@ -36115,6 +39750,11 @@
           <t>Was passiert, wenn sich die Polen immer noch nicht impfen lassen? Dr. Afelt: Wir schaden uns aus freien Stücken</t>
         </is>
       </c>
+      <c r="P728" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="n">
@@ -36164,6 +39804,11 @@
           <t>Die Linke legt einen Gesetzentwurf zur Impfpflicht vor</t>
         </is>
       </c>
+      <c r="P729" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="n">
@@ -36213,6 +39858,11 @@
           <t>Ziobro zu Covid-Zertifikaten: Ich bin kein Unterstützer</t>
         </is>
       </c>
+      <c r="P730" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="n">
@@ -36262,6 +39912,11 @@
           <t>COVID-19. Immer mehr Länder in Europa verschärfen die Impfregeln</t>
         </is>
       </c>
+      <c r="P731" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
@@ -36311,6 +39966,11 @@
           <t>Kwaśniewski zur Abtreibung: Wenn ich an der Macht wäre, würde ich dieses Gesetz etwas liberalisieren</t>
         </is>
       </c>
+      <c r="P732" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="n">
@@ -36360,6 +40020,11 @@
           <t>Dziambor verursachte einen Sturm. Ändert ein Abgeordneter der Konföderation seine Meinung zum Thema Abtreibung?</t>
         </is>
       </c>
+      <c r="P733" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
@@ -36409,6 +40074,11 @@
           <t>Was gedenkt die Kommission gegen Abtreibung in Polen zu unternehmen? Debatte im Europäischen Parlament zum Jahrestag des Urteils des Przyłębska-Tribunals</t>
         </is>
       </c>
+      <c r="P734" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="n">
@@ -36458,6 +40128,11 @@
           <t>Je mehr erneuerbare Energiequellen vorhanden sind, desto einfacher wird es für uns sein, auf Gas und Öl aus Russland zu verzichten. Die PiS-Regierung sollte aufwachen</t>
         </is>
       </c>
+      <c r="P735" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="n">
@@ -36507,6 +40182,11 @@
           <t>Die meisten Polen wollen die Rückkehr der Corona-Beschränkungen nicht, die PiS-Wähler hingegen schon</t>
         </is>
       </c>
+      <c r="P736" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="n">
@@ -36556,6 +40236,11 @@
           <t>Wird Putin Duginas Tod ausnutzen? „Der Kreml kann seine Gesellschaft beleben“</t>
         </is>
       </c>
+      <c r="P737" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="n">
@@ -36605,6 +40290,11 @@
           <t>Ziemkiewicz: Die Regierung wird wieder einmal getäuscht</t>
         </is>
       </c>
+      <c r="P738" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="n">
@@ -36654,6 +40344,11 @@
           <t>Wie ein in Ungnade gefallener Milliardär „alle glücklich machen“ will. Silvio Berlusconi kehrt in die politischen Salons zurück</t>
         </is>
       </c>
+      <c r="P739" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="n">
@@ -36703,6 +40398,11 @@
           <t>„Teflon Marek“ ist der am längsten amtierende Premierminister in der Geschichte der Niederlande. Wer ist Mark Rutte?</t>
         </is>
       </c>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="n">
@@ -36752,6 +40452,11 @@
           <t>Eine „Schwachstelle“ bei den wichtigsten Coronavirus-Varianten wurde entdeckt</t>
         </is>
       </c>
+      <c r="P741" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="n">
@@ -36801,6 +40506,11 @@
           <t>Tusk erklärt: Wir garantieren die Rechtmäßigkeit der Abtreibung bis zur 12. Woche</t>
         </is>
       </c>
+      <c r="P742" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="n">
@@ -36850,6 +40560,11 @@
           <t>Premierminister Morawiecki ist so antisemitisch, wie die Ukrainer Nazis sind</t>
         </is>
       </c>
+      <c r="P743" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="n">
@@ -36899,6 +40614,11 @@
           <t>Nicht Czarnek, nicht Najman, sondern Anna-Maria Żukowska. Der Linke-Abgeordnete gewann einen ungewöhnlichen Wettbewerb</t>
         </is>
       </c>
+      <c r="P744" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="n">
@@ -36948,6 +40668,11 @@
           <t>China hat die Geduld mit Russland verloren. „Eine beispiellose Situation“</t>
         </is>
       </c>
+      <c r="P745" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="n">
@@ -36997,6 +40722,11 @@
           <t>„Selenskys Industrie“ schweigt über den Krieg. Die Ukraine nimmt es Satirikern aus Russland übel, weil sie Putin nicht verurteilen</t>
         </is>
       </c>
+      <c r="P746" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="n">
@@ -37046,6 +40776,11 @@
           <t>In Polen wächst die Wut auf Deutschland. „Zu wenig, zu spät“</t>
         </is>
       </c>
+      <c r="P747" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="n">
@@ -37095,6 +40830,11 @@
           <t>Die militärische Lage in der Ukraine nach neun Wochen Krieg</t>
         </is>
       </c>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="n">
@@ -37144,6 +40884,11 @@
           <t>Der Krieg in der Ukraine ist eine menschliche Tragödie und eine Bedrohung für die Umwelt.</t>
         </is>
       </c>
+      <c r="P749" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="n">
@@ -37193,6 +40938,11 @@
           <t>Zwischen Narrativ und (Des-)Information: Serbische Medienberichterstattung über Russlands Aggression gegen die Ukraine.</t>
         </is>
       </c>
+      <c r="P750" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="n">
@@ -37242,6 +40992,11 @@
           <t>Krieg in der Ukraine: die neuesten Informationen.</t>
         </is>
       </c>
+      <c r="P751" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="n">
@@ -37291,6 +41046,11 @@
           <t>Kommentar: Mariupol – die Stadt der russischen Schande</t>
         </is>
       </c>
+      <c r="P752" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="n">
@@ -37340,6 +41100,11 @@
           <t>Die USA kündigten ein neues Sanktionspaket gegen Russland an</t>
         </is>
       </c>
+      <c r="P753" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="n">
@@ -37389,6 +41154,11 @@
           <t>Japan kündigte neue Sanktionen gegen Russland an</t>
         </is>
       </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="n">
@@ -37438,6 +41208,11 @@
           <t>Duma-Sprecher: Das Arsenal westlicher Sanktionen ist erschöpft. Russland kann profitieren</t>
         </is>
       </c>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="n">
@@ -37487,6 +41262,11 @@
           <t>Coronavirus – Verschwörungstheorien oder Verschwörungspraxis?</t>
         </is>
       </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="n">
@@ -37536,6 +41316,11 @@
           <t>In Italien politisiert die extreme Rechte Impfgegner</t>
         </is>
       </c>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="n">
@@ -37585,6 +41370,11 @@
           <t>COVID 19. WHO-Bericht über übermäßige Todesfälle. Lediglich Rumänien schneidet schlechter ab als Polen</t>
         </is>
       </c>
+      <c r="P758" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="n">
@@ -37634,6 +41424,11 @@
           <t>„Wir brauchen drastische Maßnahmen, denn die Welt brennt.“ Greta Thunbergs Appell</t>
         </is>
       </c>
+      <c r="P759" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="n">
@@ -37683,6 +41478,11 @@
           <t>Wahlen in Italien: Die rechtsextreme Führerin Georgia Meloni erlebt eine Welle der Unterstützung</t>
         </is>
       </c>
+      <c r="P760" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="n">
@@ -37732,6 +41532,11 @@
           <t>Russen ohne Arbeits- und Aufenthaltserlaubnis. „Es geht um Staatssicherheit“</t>
         </is>
       </c>
+      <c r="P761" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="n">
@@ -37781,6 +41586,11 @@
           <t>Irritiert Tusk die Opposition? „Funktioniert nach der Strategie von Tomasz Lis“</t>
         </is>
       </c>
+      <c r="P762" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="n">
@@ -37830,6 +41640,11 @@
           <t>Litauen „würgt“ Russland, weshalb der Krieg in den kommenden Wochen eskalieren könnte. Und wo ist Polen in all dem?</t>
         </is>
       </c>
+      <c r="P763" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="n">
@@ -37879,6 +41694,11 @@
           <t>Ja, eine Impfung ist sinnvoll, auch wenn das Virus mutiert</t>
         </is>
       </c>
+      <c r="P764" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="n">
@@ -37928,6 +41748,11 @@
           <t>Tag für Tag – eine Wirtschaftswoche mit einer Prise Salz</t>
         </is>
       </c>
+      <c r="P765" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" t="n">
@@ -37977,6 +41802,11 @@
           <t>Tag für Tag – eine Wirtschaftswoche mit einer Prise Salz, 13.-19. Mai</t>
         </is>
       </c>
+      <c r="P766" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="n">
@@ -38026,6 +41856,11 @@
           <t>KRIEGSGEIST</t>
         </is>
       </c>
+      <c r="P767" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="n">
@@ -38075,6 +41910,11 @@
           <t>Neuer stellvertretender Minister im Ministerium für Sport und Tourismus. Wer ist er?</t>
         </is>
       </c>
+      <c r="P768" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="n">
@@ -38124,6 +41964,11 @@
           <t>Die Zahl der Coronavirus-Infektionen in Polen geht weiterhin nicht zurück. Neuer Bericht des Gesundheitsministeriums</t>
         </is>
       </c>
+      <c r="P769" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="n">
@@ -38173,6 +42018,11 @@
           <t>Coronavirus. In Wuhan kommt es erneut zu einem Lockdown für Millionen Bürger. Es wurden vier Infektionsfälle festgestellt</t>
         </is>
       </c>
+      <c r="P770" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="n">
@@ -38222,6 +42072,11 @@
           <t>Joe Biden hat das Coronavirus besiegt. Der US-Präsident hat die strikte Isolation beendet und kehrt an den Arbeitsplatz zurück</t>
         </is>
       </c>
+      <c r="P771" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="n">
@@ -38271,6 +42126,11 @@
           <t>Tag für Tag – eine Wirtschaftswoche mit einer Prise Salz // 24.-30. Juni</t>
         </is>
       </c>
+      <c r="P772" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="n">
@@ -38320,6 +42180,11 @@
           <t>Tag für Tag – eine Wirtschaftswoche mit einer Prise Salz, 20.-26. Mai</t>
         </is>
       </c>
+      <c r="P773" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="n">
@@ -38369,6 +42234,11 @@
           <t>Orbán wollte erneut EU-Sanktionen torpedieren. Es gelang ihm, den russischen Parteiarchen zu beschützen</t>
         </is>
       </c>
+      <c r="P774" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="n">
@@ -38418,6 +42288,11 @@
           <t>Präsident von Brasilien: Wir werden keine Sanktionen gegen Russland verhängen. Die Ukraine wird von einem Komiker regiert</t>
         </is>
       </c>
+      <c r="P775" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="n">
@@ -38467,6 +42342,11 @@
           <t>Die Sanktionen des Westens wirken. Die russische Wirtschaft blutet</t>
         </is>
       </c>
+      <c r="P776" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="n">
@@ -38516,6 +42396,11 @@
           <t>Ist Nord Stream 2 eine „Reparationsformel“, eine „Entschädigung“ für Hitlers Verbrechen in Russland? Was der Bundespräsident wirklich gesagt hat</t>
         </is>
       </c>
+      <c r="P777" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="n">
@@ -38565,6 +42450,11 @@
           <t>Emmanuel Macron: Morawiecki mischt sich in die Wahlen in Frankreich ein</t>
         </is>
       </c>
+      <c r="P778" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="n">
@@ -38614,6 +42504,11 @@
           <t>Die NATO trifft sich, um Russland und China zu Feinden zu erklären. Ist der Dritte Weltkrieg nur eine Frage der Zeit?</t>
         </is>
       </c>
+      <c r="P779" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="n">
@@ -38663,6 +42558,11 @@
           <t>Hinter den Kulissen von Macrons Gesprächen mit Putin. Wir haben den Grund für die Invasion der Ukraine erfahren</t>
         </is>
       </c>
+      <c r="P780" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="n">
@@ -38712,6 +42612,11 @@
           <t>Der britische General analysierte das Vorgehen Russlands. „Wie Hitler vor dem Zweiten Weltkrieg“</t>
         </is>
       </c>
+      <c r="P781" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="n">
@@ -38761,6 +42666,11 @@
           <t>Ist Abtreibung ein Menschenrecht oder nicht? Darum geht es nicht</t>
         </is>
       </c>
+      <c r="P782" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="n">
@@ -38810,6 +42720,11 @@
           <t>Kataryna: Warum sollte Abtreibung moralisch neutral sein?</t>
         </is>
       </c>
+      <c r="P783" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="n">
@@ -38859,6 +42774,11 @@
           <t>Nowacka: Wir sind uns einig, Abtreibungen sind bis zur 12. Woche erlaubt</t>
         </is>
       </c>
+      <c r="P784" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="n">
@@ -38908,6 +42828,11 @@
           <t>Die Pro-Life-Stimme: Die religiösen, philosophischen, rechtlichen, biologischen und sozialen Argumente gegen Abtreibung</t>
         </is>
       </c>
+      <c r="P785" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="n">
@@ -38957,6 +42882,11 @@
           <t>TERRORISTEN AUS ORDO IURIS</t>
         </is>
       </c>
+      <c r="P786" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
@@ -39006,6 +42936,11 @@
           <t>Das chinesische Militär übt weiterhin rund um Taiwan</t>
         </is>
       </c>
+      <c r="P787" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="n">
@@ -39055,6 +42990,11 @@
           <t>Deutscher Abgeordneter: Wir müssen zu Gesprächen mit Russland über den Start von Nord Stream 2 zurückkehren</t>
         </is>
       </c>
+      <c r="P788" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
@@ -39104,6 +43044,11 @@
           <t>Ein Japaner über den Krieg in der Ukraine. Einfach schockierend…</t>
         </is>
       </c>
+      <c r="P789" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="n">
@@ -39153,6 +43098,11 @@
           <t>PiS hat Pläne für die Ukraine. Es geht sogar um die Schaffung einer „Union“ beider Länder</t>
         </is>
       </c>
+      <c r="P790" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
@@ -39202,6 +43152,11 @@
           <t>Linker Konvent. Fast alle Reden plädierten für eine Impfpflicht</t>
         </is>
       </c>
+      <c r="P791" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="n">
@@ -39251,6 +43206,11 @@
           <t>Könnten COVID-Impfungen obligatorisch sein? Rechtsgutachten des HFHR</t>
         </is>
       </c>
+      <c r="P792" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="n">
@@ -39300,6 +43260,11 @@
           <t>Nebenwirkungen nach der Novavax-Impfung gegen COVID-19</t>
         </is>
       </c>
+      <c r="P793" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="n">
@@ -39349,6 +43314,11 @@
           <t>Nordkorea: Kim Jong Un verkündete den Sieg des „sozialistischen Regimes“ über das Coronavirus</t>
         </is>
       </c>
+      <c r="P794" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="n">
@@ -39398,6 +43368,11 @@
           <t>Donald Tusk: PiS wird enden, die Preise werden enden</t>
         </is>
       </c>
+      <c r="P795" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="n">
@@ -39447,6 +43422,11 @@
           <t>Grzegorz Braun über Leben und Familie – Antworten auf Fragen für Präsidentschaftskandidaten</t>
         </is>
       </c>
+      <c r="P796" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="n">
@@ -39496,6 +43476,11 @@
           <t>Erfolg der ukrainischen Armee. Sie zerstörten ein russisches Munitionslager. Zusammenfassung der Nacht</t>
         </is>
       </c>
+      <c r="P797" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="n">
@@ -39545,6 +43530,11 @@
           <t>Schockierend! Präsident Duda: „Ich bitte Sie, ein wenig die Zähne zusammenzubeißen“</t>
         </is>
       </c>
+      <c r="P798" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="n">
@@ -39594,6 +43584,11 @@
           <t>Merkur ist in der Übersetzung verloren gegangen. Propaganda lenkt vom Versagen der Regierung an der Oder ab</t>
         </is>
       </c>
+      <c r="P799" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="n">
@@ -39643,6 +43638,11 @@
           <t>Dmitri Muratow verkaufte die Nobelmedaille für 103,5 Millionen Dollar</t>
         </is>
       </c>
+      <c r="P800" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="n">
@@ -39692,6 +43692,11 @@
           <t>Die Ukraine ist keinen Atomkrieg wert</t>
         </is>
       </c>
+      <c r="P801" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="n">
@@ -39741,6 +43746,11 @@
           <t>Verdeckt der Krieg die Pläne ruchloser Globalisten? Es ist eine Verschwörungstheorie!</t>
         </is>
       </c>
+      <c r="P802" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="n">
@@ -39790,6 +43800,11 @@
           <t>Waffennahrung auf Lager</t>
         </is>
       </c>
+      <c r="P803" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="n">
@@ -39839,6 +43854,11 @@
           <t>Es gibt Schwierigkeiten, dorthin zu gelangen, z. B. zum Wanderzirkus des Präsidenten</t>
         </is>
       </c>
+      <c r="P804" t="inlineStr">
+        <is>
+          <t>po</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="n">
@@ -39886,6 +43906,11 @@
       <c r="O805" t="inlineStr">
         <is>
           <t>Russland kann den Bankrott vermeiden. Die westliche Sanktionsmaschinerie ist offensichtlich blockiert</t>
+        </is>
+      </c>
+      <c r="P805" t="inlineStr">
+        <is>
+          <t>po</t>
         </is>
       </c>
     </row>
